--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brian\Documents\planosperu-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell Latitude\Documents\Projects\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E158348C-7360-442A-8914-8421BFFB221B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C91C58-576F-4992-97C0-4251C6D77F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
@@ -840,231 +840,152 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1097,125 +1018,204 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1658,24 +1658,38 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>        </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="002060"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>CTA BCP CUENTA CORRIENTE SOLES: 191-7674171-0-77   </a:t>
+            <a:t>CTA BCP CUENTA CORRIENTE SOLES: 191-7674171-0-77  CCI: 00219100767417107756</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1697,26 +1711,21 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="002060"/>
               </a:solidFill>
               <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>CCI: 00219100767417107756 T</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>itular Ing. Atapaucar Bardales Richard</a:t>
+            <a:t>Cuenta BBVA: Número de cuenta: 0011-0814-0278938730   CCI: 0118140002789387</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1738,49 +1747,119 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr kumimoji="0" lang="es-PE" sz="900" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
               <a:solidFill>
                 <a:srgbClr val="002060"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Se aceptan todo tipo de Tarjetas de Credito</a:t>
+            <a:t>Titular Ing. Atapaucar Bardales Richard. Se aceptan todo tipo de Tarjetas de Credito</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l" rtl="0">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="es-PE" sz="1150" b="1" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr kumimoji="0" lang="es-PE" sz="1150" b="1" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:srgbClr val="FFFFFF"/>
             </a:solidFill>
+            <a:effectLst/>
+            <a:uLnTx/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
+            <a:ea typeface="+mn-ea"/>
             <a:cs typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="l" rtl="0">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr kumimoji="0" lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
+            <a:effectLst/>
+            <a:uLnTx/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
+            <a:ea typeface="+mn-ea"/>
             <a:cs typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="l" rtl="0">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr kumimoji="0" lang="es-PE" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
+            <a:effectLst/>
+            <a:uLnTx/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
+            <a:ea typeface="+mn-ea"/>
             <a:cs typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
@@ -1880,9 +1959,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1920,7 +1999,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2026,7 +2105,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2168,7 +2247,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2181,7 +2260,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:H80"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
@@ -2200,86 +2279,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="144" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="145" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="146" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
+      <c r="A8" s="148"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
+      <c r="C9" s="143"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="143"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
+      <c r="B10" s="143"/>
+      <c r="C10" s="143"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="143"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2288,22 +2367,22 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2328,10 +2407,10 @@
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
       <c r="F15" s="13" t="s">
         <v>13</v>
       </c>
@@ -2340,10 +2419,10 @@
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
+      <c r="B16" s="132"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
       <c r="F16" s="13" t="s">
         <v>14</v>
       </c>
@@ -2354,14 +2433,14 @@
       <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
       <c r="D17" s="18" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="19">
         <f ca="1">TODAY()</f>
-        <v>45870</v>
+        <v>45973</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2369,169 +2448,169 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="136"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
       <c r="H19" s="22"/>
     </row>
     <row r="20" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="65" t="s">
+      <c r="C20" s="139"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="65"/>
-      <c r="G20" s="66"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="142"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="53" t="s">
+      <c r="C21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="54"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="128"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="70"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="130"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="52" t="s">
+      <c r="C23" s="127"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="54"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="128"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="52" t="s">
+      <c r="C24" s="127"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="53"/>
-      <c r="G24" s="54"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="128"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="53"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="71" t="s">
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="72"/>
-      <c r="G25" s="73"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="67"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="52" t="s">
+      <c r="C26" s="127"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="54"/>
+      <c r="F26" s="127"/>
+      <c r="G26" s="128"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="75"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="52" t="s">
+      <c r="C27" s="83"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="54"/>
+      <c r="F27" s="127"/>
+      <c r="G27" s="128"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="85"/>
-      <c r="E28" s="86" t="s">
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="87"/>
-      <c r="G28" s="88"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="114"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="116"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
-      <c r="B30" s="91" t="s">
+      <c r="B30" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="93"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="119"/>
       <c r="E30" s="30" t="s">
         <v>37</v>
       </c>
@@ -2541,11 +2620,11 @@
     </row>
     <row r="31" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="81"/>
-      <c r="D31" s="82"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="99"/>
       <c r="E31" s="26" t="s">
         <v>39</v>
       </c>
@@ -2555,11 +2634,11 @@
     </row>
     <row r="32" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="95"/>
-      <c r="D32" s="96"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="122"/>
       <c r="E32" s="26" t="s">
         <v>41</v>
       </c>
@@ -2569,89 +2648,89 @@
     </row>
     <row r="33" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="95"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="74" t="s">
+      <c r="B33" s="120"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="122"/>
+      <c r="E33" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="75"/>
-      <c r="G33" s="76"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="84"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="74" t="s">
+      <c r="C34" s="83"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="75"/>
-      <c r="G34" s="76"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="84"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="98"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="74" t="s">
+      <c r="C35" s="124"/>
+      <c r="D35" s="125"/>
+      <c r="E35" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="75"/>
-      <c r="G35" s="76"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="84"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="80" t="s">
+      <c r="B36" s="123"/>
+      <c r="C36" s="124"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="F36" s="81"/>
-      <c r="G36" s="82"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="99"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="74" t="s">
+      <c r="B37" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="75"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="77" t="s">
+      <c r="C37" s="83"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="78"/>
-      <c r="G37" s="79"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="108"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="80" t="s">
+      <c r="B38" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="81"/>
-      <c r="D38" s="82"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="79"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="108"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="80" t="s">
+      <c r="B39" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="81"/>
-      <c r="D39" s="82"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="99"/>
       <c r="E39" s="100" t="s">
         <v>52</v>
       </c>
@@ -2661,11 +2740,11 @@
     </row>
     <row r="40" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="81"/>
-      <c r="D40" s="82"/>
+      <c r="C40" s="98"/>
+      <c r="D40" s="99"/>
       <c r="E40" s="103" t="s">
         <v>54</v>
       </c>
@@ -2675,141 +2754,141 @@
     </row>
     <row r="41" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="81"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="77" t="s">
+      <c r="C41" s="98"/>
+      <c r="D41" s="99"/>
+      <c r="E41" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="F41" s="78"/>
-      <c r="G41" s="79"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="108"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="80" t="s">
+      <c r="B42" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="81"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="79"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="99"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="107"/>
+      <c r="G42" s="108"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="74" t="s">
+      <c r="B43" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="106" t="s">
+      <c r="C43" s="83"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="F43" s="107"/>
-      <c r="G43" s="108"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="87"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="74" t="s">
+      <c r="B44" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="109"/>
-      <c r="F44" s="110"/>
-      <c r="G44" s="111"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="84"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="90"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="112" t="s">
+      <c r="B45" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="113"/>
-      <c r="D45" s="114"/>
-      <c r="E45" s="115"/>
-      <c r="F45" s="116"/>
-      <c r="G45" s="117"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="96"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="67" t="s">
+      <c r="B46" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="120"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="61"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="121" t="s">
+      <c r="B47" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="123"/>
-      <c r="E47" s="71" t="s">
+      <c r="C47" s="63"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="72"/>
-      <c r="G47" s="73"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="67"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="124" t="s">
+      <c r="B48" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="125"/>
-      <c r="D48" s="126"/>
-      <c r="E48" s="124" t="s">
+      <c r="C48" s="69"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="F48" s="125"/>
-      <c r="G48" s="126"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="124" t="s">
+      <c r="B49" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="125"/>
-      <c r="D49" s="126"/>
-      <c r="E49" s="127" t="s">
+      <c r="C49" s="69"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="F49" s="128"/>
-      <c r="G49" s="129"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="73"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="130" t="s">
+      <c r="B50" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="131"/>
-      <c r="D50" s="132"/>
-      <c r="E50" s="133"/>
-      <c r="F50" s="134"/>
-      <c r="G50" s="135"/>
+      <c r="C50" s="75"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="78"/>
+      <c r="G50" s="79"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="136"/>
-      <c r="C51" s="136"/>
-      <c r="D51" s="136"/>
-      <c r="E51" s="136"/>
-      <c r="F51" s="136"/>
-      <c r="G51" s="136"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2817,61 +2896,61 @@
       <c r="B52" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="137"/>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137"/>
-      <c r="F52" s="137"/>
-      <c r="G52" s="137"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="118"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="118"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="118"/>
-      <c r="G54" s="118"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="139"/>
-      <c r="C55" s="139"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
-      <c r="B56" s="140" t="s">
+      <c r="B56" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="C56" s="140"/>
-      <c r="D56" s="140"/>
-      <c r="E56" s="140"/>
-      <c r="F56" s="140"/>
-      <c r="G56" s="140"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
       <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
-      <c r="B57" s="141" t="s">
+      <c r="B57" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="141"/>
+      <c r="C57" s="51"/>
       <c r="D57" s="35">
         <v>6</v>
       </c>
@@ -2884,43 +2963,43 @@
     </row>
     <row r="58" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
-      <c r="B58" s="140" t="s">
+      <c r="B58" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="140"/>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="140"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
-      <c r="B59" s="142" t="s">
+      <c r="B59" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="142"/>
+      <c r="C59" s="52"/>
       <c r="D59" s="37">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="143" t="s">
+      <c r="E59" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="F59" s="143"/>
+      <c r="F59" s="53"/>
       <c r="G59" s="20"/>
       <c r="H59" s="22"/>
     </row>
     <row r="60" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
-      <c r="B60" s="140" t="s">
+      <c r="B60" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="140"/>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="140"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="50"/>
+      <c r="E60" s="50"/>
+      <c r="F60" s="50"/>
+      <c r="G60" s="50"/>
       <c r="H60" s="22"/>
     </row>
     <row r="61" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2929,14 +3008,14 @@
         <v>91</v>
       </c>
       <c r="C61" s="38"/>
-      <c r="D61" s="144" t="s">
+      <c r="D61" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="145"/>
-      <c r="F61" s="145"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="39">
         <f ca="1">E$17</f>
-        <v>45870</v>
+        <v>45973</v>
       </c>
       <c r="H61" s="22"/>
     </row>
@@ -2946,14 +3025,14 @@
         <v>92</v>
       </c>
       <c r="C62" s="40"/>
-      <c r="D62" s="145" t="s">
+      <c r="D62" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="E62" s="145"/>
-      <c r="F62" s="145"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="55"/>
       <c r="G62" s="39">
         <f ca="1">E$17+8</f>
-        <v>45878</v>
+        <v>45981</v>
       </c>
       <c r="H62" s="22"/>
     </row>
@@ -2963,14 +3042,14 @@
         <v>93</v>
       </c>
       <c r="C63" s="40"/>
-      <c r="D63" s="145" t="s">
+      <c r="D63" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="E63" s="145"/>
-      <c r="F63" s="145"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="55"/>
       <c r="G63" s="39">
         <f ca="1">E$17+35</f>
-        <v>45905</v>
+        <v>46008</v>
       </c>
       <c r="H63" s="41" t="s">
         <v>80</v>
@@ -2978,77 +3057,77 @@
     </row>
     <row r="64" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="146" t="s">
+      <c r="B64" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="146"/>
-      <c r="D64" s="146"/>
-      <c r="E64" s="146"/>
-      <c r="F64" s="146"/>
-      <c r="G64" s="146"/>
+      <c r="C64" s="56"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
       <c r="H64" s="42"/>
     </row>
     <row r="65" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="B65" s="138" t="s">
+      <c r="B65" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="C65" s="138"/>
-      <c r="D65" s="138"/>
-      <c r="E65" s="138"/>
-      <c r="F65" s="138"/>
-      <c r="G65" s="138"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="147" t="s">
+      <c r="B66" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C66" s="147"/>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147" t="s">
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="G66" s="147"/>
-      <c r="H66" s="147"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="46"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="148" t="s">
+      <c r="B67" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="148"/>
-      <c r="D67" s="148"/>
-      <c r="E67" s="148"/>
-      <c r="F67" s="147" t="s">
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="G67" s="147"/>
-      <c r="H67" s="147"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="148" t="s">
+      <c r="B68" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="148"/>
-      <c r="D68" s="148"/>
-      <c r="E68" s="148"/>
-      <c r="F68" s="147" t="s">
+      <c r="C68" s="47"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="G68" s="147"/>
-      <c r="H68" s="147"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="147" t="s">
+      <c r="B69" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="147"/>
-      <c r="D69" s="147"/>
-      <c r="E69" s="147"/>
-      <c r="F69" s="147"/>
-      <c r="G69" s="147"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="46"/>
+      <c r="G69" s="46"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="44"/>
@@ -3075,52 +3154,37 @@
     <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2"/>
   </protectedRanges>
   <mergeCells count="92">
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E37:G38"/>
     <mergeCell ref="B38:D38"/>
@@ -3136,44 +3200,59 @@
     <mergeCell ref="B35:D36"/>
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell Latitude\Documents\Projects\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\planos_peru_intranet\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C91C58-576F-4992-97C0-4251C6D77F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DFEFE1-68F8-4C1C-BFA5-4798F44A5E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -840,45 +840,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -888,104 +919,152 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1018,201 +1097,122 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2279,86 +2279,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="145" t="s">
+      <c r="D5" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="146" t="s">
+      <c r="D6" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="146"/>
-      <c r="F6" s="146"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="147" t="s">
+      <c r="D7" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="148"/>
-      <c r="B8" s="148"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="148"/>
-      <c r="E8" s="148"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="148"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="143" t="s">
+      <c r="B9" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="143"/>
-      <c r="D9" s="143"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="143"/>
-      <c r="G9" s="143"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="143"/>
-      <c r="C10" s="143"/>
-      <c r="D10" s="143"/>
-      <c r="E10" s="143"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="143"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="131" t="s">
+      <c r="B11" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2407,10 +2407,10 @@
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="F15" s="13" t="s">
         <v>13</v>
       </c>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="132"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
       <c r="F16" s="13" t="s">
         <v>14</v>
       </c>
@@ -2433,14 +2433,14 @@
       <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="131"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="18" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="19">
         <f ca="1">TODAY()</f>
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2448,169 +2448,169 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="133"/>
-      <c r="C18" s="133"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
-      <c r="B19" s="134" t="s">
+      <c r="B19" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="135"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="137"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
       <c r="H19" s="22"/>
     </row>
     <row r="20" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="138" t="s">
+      <c r="B20" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="139"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141" t="s">
+      <c r="C20" s="63"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="141"/>
-      <c r="G20" s="142"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="126" t="s">
+      <c r="B21" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="127" t="s">
+      <c r="C21" s="53"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="127"/>
-      <c r="G21" s="128"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="54"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="130"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="70"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="126" t="s">
+      <c r="B23" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="127"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="126" t="s">
+      <c r="C23" s="53"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="127"/>
-      <c r="G23" s="128"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="54"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="126" t="s">
+      <c r="B24" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="127"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="126" t="s">
+      <c r="C24" s="53"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="127"/>
-      <c r="G24" s="128"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="54"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="126" t="s">
+      <c r="B25" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="65" t="s">
+      <c r="C25" s="53"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="66"/>
-      <c r="G25" s="67"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="73"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="126" t="s">
+      <c r="B26" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="127"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="126" t="s">
+      <c r="C26" s="53"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="127"/>
-      <c r="G26" s="128"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="54"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="82" t="s">
+      <c r="B27" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="83"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="126" t="s">
+      <c r="C27" s="75"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="127"/>
-      <c r="G27" s="128"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="54"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="109" t="s">
+      <c r="B28" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="110"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112" t="s">
+      <c r="C28" s="84"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="113"/>
-      <c r="G28" s="114"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="88"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="116"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
-      <c r="B30" s="117" t="s">
+      <c r="B30" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="119"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="93"/>
       <c r="E30" s="30" t="s">
         <v>37</v>
       </c>
@@ -2620,11 +2620,11 @@
     </row>
     <row r="31" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
-      <c r="B31" s="97" t="s">
+      <c r="B31" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="98"/>
-      <c r="D31" s="99"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="82"/>
       <c r="E31" s="26" t="s">
         <v>39</v>
       </c>
@@ -2634,11 +2634,11 @@
     </row>
     <row r="32" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
-      <c r="B32" s="120" t="s">
+      <c r="B32" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="122"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="96"/>
       <c r="E32" s="26" t="s">
         <v>41</v>
       </c>
@@ -2648,89 +2648,89 @@
     </row>
     <row r="33" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="120"/>
-      <c r="C33" s="121"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="82" t="s">
+      <c r="B33" s="94"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="83"/>
-      <c r="G33" s="84"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="82" t="s">
+      <c r="B34" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="83"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="82" t="s">
+      <c r="C34" s="75"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="83"/>
-      <c r="G34" s="84"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="76"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="123" t="s">
+      <c r="B35" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="124"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="82" t="s">
+      <c r="C35" s="98"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="83"/>
-      <c r="G35" s="84"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="76"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="123"/>
-      <c r="C36" s="124"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="97" t="s">
+      <c r="B36" s="97"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="F36" s="98"/>
-      <c r="G36" s="99"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="82"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="82" t="s">
+      <c r="B37" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="83"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="106" t="s">
+      <c r="C37" s="75"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="107"/>
-      <c r="G37" s="108"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="79"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="97" t="s">
+      <c r="B38" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="98"/>
-      <c r="D38" s="99"/>
-      <c r="E38" s="106"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="108"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="79"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="97" t="s">
+      <c r="B39" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="98"/>
-      <c r="D39" s="99"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="82"/>
       <c r="E39" s="100" t="s">
         <v>52</v>
       </c>
@@ -2740,11 +2740,11 @@
     </row>
     <row r="40" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="97" t="s">
+      <c r="B40" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="98"/>
-      <c r="D40" s="99"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="82"/>
       <c r="E40" s="103" t="s">
         <v>54</v>
       </c>
@@ -2754,141 +2754,141 @@
     </row>
     <row r="41" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="97" t="s">
+      <c r="B41" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="98"/>
-      <c r="D41" s="99"/>
-      <c r="E41" s="106" t="s">
+      <c r="C41" s="81"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="F41" s="107"/>
-      <c r="G41" s="108"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="79"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="97" t="s">
+      <c r="B42" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="98"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="107"/>
-      <c r="G42" s="108"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="79"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="82" t="s">
+      <c r="B43" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="83"/>
-      <c r="D43" s="84"/>
-      <c r="E43" s="85" t="s">
+      <c r="C43" s="75"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="F43" s="86"/>
-      <c r="G43" s="87"/>
+      <c r="F43" s="107"/>
+      <c r="G43" s="108"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="83"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="90"/>
+      <c r="C44" s="75"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="109"/>
+      <c r="F44" s="110"/>
+      <c r="G44" s="111"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="91" t="s">
+      <c r="B45" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="94"/>
-      <c r="F45" s="95"/>
-      <c r="G45" s="96"/>
+      <c r="C45" s="113"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="115"/>
+      <c r="F45" s="116"/>
+      <c r="G45" s="117"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="61"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="119"/>
+      <c r="G46" s="120"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="62" t="s">
+      <c r="B47" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="63"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65" t="s">
+      <c r="C47" s="122"/>
+      <c r="D47" s="123"/>
+      <c r="E47" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="66"/>
-      <c r="G47" s="67"/>
+      <c r="F47" s="72"/>
+      <c r="G47" s="73"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="68" t="s">
+      <c r="B48" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="69"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="68" t="s">
+      <c r="C48" s="125"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="F48" s="125"/>
+      <c r="G48" s="126"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="71" t="s">
+      <c r="C49" s="125"/>
+      <c r="D49" s="126"/>
+      <c r="E49" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="F49" s="72"/>
-      <c r="G49" s="73"/>
+      <c r="F49" s="128"/>
+      <c r="G49" s="129"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="74" t="s">
+      <c r="B50" s="130" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="75"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="79"/>
+      <c r="C50" s="131"/>
+      <c r="D50" s="132"/>
+      <c r="E50" s="133"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="135"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="80"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="80"/>
+      <c r="B51" s="136"/>
+      <c r="C51" s="136"/>
+      <c r="D51" s="136"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="136"/>
+      <c r="G51" s="136"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2896,61 +2896,61 @@
       <c r="B52" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
+      <c r="C52" s="137"/>
+      <c r="D52" s="137"/>
+      <c r="E52" s="137"/>
+      <c r="F52" s="137"/>
+      <c r="G52" s="137"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
+      <c r="B53" s="118"/>
+      <c r="C53" s="118"/>
+      <c r="D53" s="118"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="57"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="57"/>
-      <c r="E54" s="57"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
+      <c r="B54" s="118"/>
+      <c r="C54" s="118"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="118"/>
+      <c r="F54" s="118"/>
+      <c r="G54" s="118"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
+      <c r="B55" s="139"/>
+      <c r="C55" s="139"/>
+      <c r="D55" s="139"/>
+      <c r="E55" s="139"/>
+      <c r="F55" s="139"/>
+      <c r="G55" s="139"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
-      <c r="B56" s="50" t="s">
+      <c r="B56" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="C56" s="140"/>
+      <c r="D56" s="140"/>
+      <c r="E56" s="140"/>
+      <c r="F56" s="140"/>
+      <c r="G56" s="140"/>
       <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="141" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="51"/>
+      <c r="C57" s="141"/>
       <c r="D57" s="35">
         <v>6</v>
       </c>
@@ -2963,43 +2963,43 @@
     </row>
     <row r="58" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
-      <c r="B58" s="50" t="s">
+      <c r="B58" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="50"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
+      <c r="C58" s="140"/>
+      <c r="D58" s="140"/>
+      <c r="E58" s="140"/>
+      <c r="F58" s="140"/>
+      <c r="G58" s="140"/>
       <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
-      <c r="B59" s="52" t="s">
+      <c r="B59" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="52"/>
+      <c r="C59" s="142"/>
       <c r="D59" s="37">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="53" t="s">
+      <c r="E59" s="143" t="s">
         <v>76</v>
       </c>
-      <c r="F59" s="53"/>
+      <c r="F59" s="143"/>
       <c r="G59" s="20"/>
       <c r="H59" s="22"/>
     </row>
     <row r="60" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
-      <c r="B60" s="50" t="s">
+      <c r="B60" s="140" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="50"/>
-      <c r="D60" s="50"/>
-      <c r="E60" s="50"/>
-      <c r="F60" s="50"/>
-      <c r="G60" s="50"/>
+      <c r="C60" s="140"/>
+      <c r="D60" s="140"/>
+      <c r="E60" s="140"/>
+      <c r="F60" s="140"/>
+      <c r="G60" s="140"/>
       <c r="H60" s="22"/>
     </row>
     <row r="61" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -3008,14 +3008,14 @@
         <v>91</v>
       </c>
       <c r="C61" s="38"/>
-      <c r="D61" s="54" t="s">
+      <c r="D61" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="55"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="145"/>
+      <c r="F61" s="145"/>
       <c r="G61" s="39">
         <f ca="1">E$17</f>
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="H61" s="22"/>
     </row>
@@ -3025,14 +3025,14 @@
         <v>92</v>
       </c>
       <c r="C62" s="40"/>
-      <c r="D62" s="55" t="s">
+      <c r="D62" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="E62" s="55"/>
-      <c r="F62" s="55"/>
+      <c r="E62" s="145"/>
+      <c r="F62" s="145"/>
       <c r="G62" s="39">
         <f ca="1">E$17+8</f>
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H62" s="22"/>
     </row>
@@ -3042,14 +3042,14 @@
         <v>93</v>
       </c>
       <c r="C63" s="40"/>
-      <c r="D63" s="55" t="s">
+      <c r="D63" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="E63" s="55"/>
-      <c r="F63" s="55"/>
+      <c r="E63" s="145"/>
+      <c r="F63" s="145"/>
       <c r="G63" s="39">
         <f ca="1">E$17+35</f>
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="H63" s="41" t="s">
         <v>80</v>
@@ -3057,77 +3057,77 @@
     </row>
     <row r="64" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="56" t="s">
+      <c r="B64" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="56"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="56"/>
-      <c r="F64" s="56"/>
-      <c r="G64" s="56"/>
+      <c r="C64" s="146"/>
+      <c r="D64" s="146"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="146"/>
       <c r="H64" s="42"/>
     </row>
     <row r="65" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="B65" s="48" t="s">
+      <c r="B65" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
+      <c r="C65" s="138"/>
+      <c r="D65" s="138"/>
+      <c r="E65" s="138"/>
+      <c r="F65" s="138"/>
+      <c r="G65" s="138"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="46" t="s">
+      <c r="B66" s="147" t="s">
         <v>94</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46" t="s">
+      <c r="C66" s="147"/>
+      <c r="D66" s="147"/>
+      <c r="E66" s="147"/>
+      <c r="F66" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
+      <c r="G66" s="147"/>
+      <c r="H66" s="147"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="148" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="46" t="s">
+      <c r="C67" s="148"/>
+      <c r="D67" s="148"/>
+      <c r="E67" s="148"/>
+      <c r="F67" s="147" t="s">
         <v>86</v>
       </c>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
+      <c r="G67" s="147"/>
+      <c r="H67" s="147"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="47" t="s">
+      <c r="B68" s="148" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="47"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="46" t="s">
+      <c r="C68" s="148"/>
+      <c r="D68" s="148"/>
+      <c r="E68" s="148"/>
+      <c r="F68" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
+      <c r="G68" s="147"/>
+      <c r="H68" s="147"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="46" t="s">
+      <c r="B69" s="147" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
+      <c r="C69" s="147"/>
+      <c r="D69" s="147"/>
+      <c r="E69" s="147"/>
+      <c r="F69" s="147"/>
+      <c r="G69" s="147"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="44"/>
@@ -3154,37 +3154,52 @@
     <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2"/>
   </protectedRanges>
   <mergeCells count="92">
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E37:G38"/>
     <mergeCell ref="B38:D38"/>
@@ -3200,59 +3215,44 @@
     <mergeCell ref="B35:D36"/>
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\planos_peru_intranet\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Documents\git\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DFEFE1-68F8-4C1C-BFA5-4798F44A5E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EA6226-D8C0-446D-B10E-7C23D1B13B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -77,9 +77,6 @@
     <t>Medidas:</t>
   </si>
   <si>
-    <t>Cliente (a)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ubicación: </t>
   </si>
   <si>
@@ -326,9 +323,6 @@
     <t>Ing. Aguirre Alanya Luis Antonio CIP: 323997 CIV: 022178VCZRIX</t>
   </si>
   <si>
-    <t>Pisos:</t>
-  </si>
-  <si>
     <t>www.planosperu.com.pe</t>
   </si>
   <si>
@@ -339,6 +333,12 @@
   </si>
   <si>
     <t>Av. Guillermo Billinghurst 1081, Oficina 202 - SJM</t>
+  </si>
+  <si>
+    <t>Niveles:</t>
+  </si>
+  <si>
+    <t>Solicitante:</t>
   </si>
 </sst>
 </file>
@@ -840,231 +840,152 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1097,122 +1018,201 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2279,86 +2279,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
+      <c r="D4" s="144" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
+      <c r="D5" s="145" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
+      <c r="D6" s="146" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="D7" s="147" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
+      <c r="A8" s="148"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
+      <c r="C9" s="143"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="143"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
+      <c r="B10" s="143"/>
+      <c r="C10" s="143"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="143"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2367,27 +2367,27 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B14" s="45"/>
       <c r="C14" s="13" t="s">
@@ -2405,42 +2405,42 @@
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="131"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="13" t="s">
         <v>12</v>
-      </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="13" t="s">
-        <v>13</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
+      <c r="B16" s="132"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
       <c r="F16" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="18" t="s">
         <v>15</v>
-      </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="18" t="s">
-        <v>16</v>
       </c>
       <c r="E17" s="19">
         <f ca="1">TODAY()</f>
-        <v>45974</v>
+        <v>46071</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2448,171 +2448,171 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
-      <c r="B19" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
+      <c r="B19" s="134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="135"/>
+      <c r="D19" s="136"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
       <c r="H19" s="22"/>
     </row>
     <row r="20" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="138" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="139"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="65"/>
-      <c r="G20" s="66"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="142"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="126" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="54"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="128"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="70"/>
+      <c r="B22" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="130"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="126" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="127"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="54"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="128"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="127"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="53"/>
-      <c r="G24" s="54"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="128"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="53"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="72"/>
-      <c r="G25" s="73"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="67"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="126" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="127"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="54"/>
+      <c r="F26" s="127"/>
+      <c r="G26" s="128"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="83"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="75"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="54"/>
+      <c r="F27" s="127"/>
+      <c r="G27" s="128"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="85"/>
-      <c r="E28" s="86" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="87"/>
-      <c r="G28" s="88"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="114"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
+      <c r="B29" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="116"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
-      <c r="B30" s="91" t="s">
+      <c r="B30" s="117" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="118"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="30" t="s">
         <v>36</v>
-      </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="30" t="s">
-        <v>37</v>
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="31" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="97" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="98"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="26" t="s">
         <v>38</v>
-      </c>
-      <c r="C31" s="81"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="26" t="s">
-        <v>39</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="28"/>
@@ -2634,13 +2634,13 @@
     </row>
     <row r="32" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="120" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="121"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="26" t="s">
         <v>40</v>
-      </c>
-      <c r="C32" s="95"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="26" t="s">
-        <v>41</v>
       </c>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
@@ -2648,91 +2648,91 @@
     </row>
     <row r="33" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="95"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="75"/>
-      <c r="G33" s="76"/>
+      <c r="B33" s="120"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="122"/>
+      <c r="E33" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="83"/>
+      <c r="G33" s="84"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="82" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="83"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="75"/>
-      <c r="G34" s="76"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="84"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="123" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="124"/>
+      <c r="D35" s="125"/>
+      <c r="E35" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="98"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" s="75"/>
-      <c r="G35" s="76"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="84"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="80" t="s">
-        <v>47</v>
-      </c>
-      <c r="F36" s="81"/>
-      <c r="G36" s="82"/>
+      <c r="B36" s="123"/>
+      <c r="C36" s="124"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="98"/>
+      <c r="G36" s="99"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="74" t="s">
+      <c r="B37" s="82" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="83"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="75"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="77" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="78"/>
-      <c r="G37" s="79"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="108"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="80" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="81"/>
-      <c r="D38" s="82"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="79"/>
+      <c r="B38" s="97" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="98"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="108"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="80" t="s">
+      <c r="B39" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="98"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="100" t="s">
         <v>51</v>
-      </c>
-      <c r="C39" s="81"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="100" t="s">
-        <v>52</v>
       </c>
       <c r="F39" s="101"/>
       <c r="G39" s="102"/>
@@ -2740,13 +2740,13 @@
     </row>
     <row r="40" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="98"/>
+      <c r="D40" s="99"/>
+      <c r="E40" s="103" t="s">
         <v>53</v>
-      </c>
-      <c r="C40" s="81"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="103" t="s">
-        <v>54</v>
       </c>
       <c r="F40" s="104"/>
       <c r="G40" s="105"/>
@@ -2754,208 +2754,208 @@
     </row>
     <row r="41" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="97" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="98"/>
+      <c r="D41" s="99"/>
+      <c r="E41" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="81"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="77" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" s="78"/>
-      <c r="G41" s="79"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="108"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="C42" s="81"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="79"/>
+      <c r="B42" s="97" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="98"/>
+      <c r="D42" s="99"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="107"/>
+      <c r="G42" s="108"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="74" t="s">
+      <c r="B43" s="82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="83"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="106" t="s">
-        <v>59</v>
-      </c>
-      <c r="F43" s="107"/>
-      <c r="G43" s="108"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="87"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="74" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="109"/>
-      <c r="F44" s="110"/>
-      <c r="G44" s="111"/>
+      <c r="B44" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" s="83"/>
+      <c r="D44" s="84"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="90"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="112" t="s">
+      <c r="B45" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="92"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="10"/>
+    </row>
+    <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="113"/>
-      <c r="D45" s="114"/>
-      <c r="E45" s="115"/>
-      <c r="F45" s="116"/>
-      <c r="G45" s="117"/>
-      <c r="H45" s="10"/>
-    </row>
-    <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="67" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="120"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="61"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="121" t="s">
+      <c r="B47" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="63"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="123"/>
-      <c r="E47" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47" s="72"/>
-      <c r="G47" s="73"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="67"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="124" t="s">
+      <c r="B48" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="69"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="125"/>
-      <c r="D48" s="126"/>
-      <c r="E48" s="124" t="s">
-        <v>66</v>
-      </c>
-      <c r="F48" s="125"/>
-      <c r="G48" s="126"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="124" t="s">
+      <c r="B49" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="69"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="125"/>
-      <c r="D49" s="126"/>
-      <c r="E49" s="127" t="s">
-        <v>68</v>
-      </c>
-      <c r="F49" s="128"/>
-      <c r="G49" s="129"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="73"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="130" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" s="131"/>
-      <c r="D50" s="132"/>
-      <c r="E50" s="133"/>
-      <c r="F50" s="134"/>
-      <c r="G50" s="135"/>
+      <c r="B50" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="75"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="78"/>
+      <c r="G50" s="79"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="136"/>
-      <c r="C51" s="136"/>
-      <c r="D51" s="136"/>
-      <c r="E51" s="136"/>
-      <c r="F51" s="136"/>
-      <c r="G51" s="136"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10"/>
       <c r="B52" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="137"/>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137"/>
-      <c r="F52" s="137"/>
-      <c r="G52" s="137"/>
+        <v>69</v>
+      </c>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="118"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="118"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="118"/>
-      <c r="G54" s="118"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="139"/>
-      <c r="C55" s="139"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
-      <c r="B56" s="140" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="140"/>
-      <c r="D56" s="140"/>
-      <c r="E56" s="140"/>
-      <c r="F56" s="140"/>
-      <c r="G56" s="140"/>
+      <c r="B56" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
       <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
-      <c r="B57" s="141" t="s">
-        <v>72</v>
-      </c>
-      <c r="C57" s="141"/>
+      <c r="B57" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="51"/>
       <c r="D57" s="35">
         <v>6</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
@@ -2963,171 +2963,171 @@
     </row>
     <row r="58" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
-      <c r="B58" s="140" t="s">
-        <v>74</v>
-      </c>
-      <c r="C58" s="140"/>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="140"/>
+      <c r="B58" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
-      <c r="B59" s="142" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="142"/>
+      <c r="B59" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" s="52"/>
       <c r="D59" s="37">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="143" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59" s="143"/>
+      <c r="E59" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" s="53"/>
       <c r="G59" s="20"/>
       <c r="H59" s="22"/>
     </row>
     <row r="60" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
-      <c r="B60" s="140" t="s">
-        <v>77</v>
-      </c>
-      <c r="C60" s="140"/>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="140"/>
+      <c r="B60" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="50"/>
+      <c r="D60" s="50"/>
+      <c r="E60" s="50"/>
+      <c r="F60" s="50"/>
+      <c r="G60" s="50"/>
       <c r="H60" s="22"/>
     </row>
     <row r="61" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22"/>
       <c r="B61" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C61" s="38"/>
-      <c r="D61" s="144" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" s="145"/>
-      <c r="F61" s="145"/>
+      <c r="D61" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="55"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="39">
         <f ca="1">E$17</f>
-        <v>45974</v>
+        <v>46071</v>
       </c>
       <c r="H61" s="22"/>
     </row>
     <row r="62" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="22"/>
       <c r="B62" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C62" s="40"/>
-      <c r="D62" s="145" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62" s="145"/>
-      <c r="F62" s="145"/>
+      <c r="D62" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" s="55"/>
+      <c r="F62" s="55"/>
       <c r="G62" s="39">
         <f ca="1">E$17+8</f>
-        <v>45982</v>
+        <v>46079</v>
       </c>
       <c r="H62" s="22"/>
     </row>
     <row r="63" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="22"/>
       <c r="B63" s="36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C63" s="40"/>
-      <c r="D63" s="145" t="s">
-        <v>79</v>
-      </c>
-      <c r="E63" s="145"/>
-      <c r="F63" s="145"/>
+      <c r="D63" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" s="55"/>
+      <c r="F63" s="55"/>
       <c r="G63" s="39">
         <f ca="1">E$17+35</f>
-        <v>46009</v>
+        <v>46106</v>
       </c>
       <c r="H63" s="41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="146" t="s">
-        <v>81</v>
-      </c>
-      <c r="C64" s="146"/>
-      <c r="D64" s="146"/>
-      <c r="E64" s="146"/>
-      <c r="F64" s="146"/>
-      <c r="G64" s="146"/>
+      <c r="B64" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C64" s="56"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
       <c r="H64" s="42"/>
     </row>
     <row r="65" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="B65" s="138" t="s">
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+    </row>
+    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C65" s="138"/>
-      <c r="D65" s="138"/>
-      <c r="E65" s="138"/>
-      <c r="F65" s="138"/>
-      <c r="G65" s="138"/>
-    </row>
-    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="147" t="s">
-        <v>94</v>
-      </c>
-      <c r="C66" s="147"/>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147" t="s">
+      <c r="G66" s="46"/>
+      <c r="H66" s="46"/>
+    </row>
+    <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="G66" s="147"/>
-      <c r="H66" s="147"/>
-    </row>
-    <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="148" t="s">
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="148"/>
-      <c r="D67" s="148"/>
-      <c r="E67" s="148"/>
-      <c r="F67" s="147" t="s">
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
+    </row>
+    <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="G67" s="147"/>
-      <c r="H67" s="147"/>
-    </row>
-    <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="148" t="s">
+      <c r="C68" s="47"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="148"/>
-      <c r="D68" s="148"/>
-      <c r="E68" s="148"/>
-      <c r="F68" s="147" t="s">
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
+    </row>
+    <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="G68" s="147"/>
-      <c r="H68" s="147"/>
-    </row>
-    <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="147" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="147"/>
-      <c r="D69" s="147"/>
-      <c r="E69" s="147"/>
-      <c r="F69" s="147"/>
-      <c r="G69" s="147"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="46"/>
+      <c r="G69" s="46"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="44"/>
@@ -3154,52 +3154,37 @@
     <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2"/>
   </protectedRanges>
   <mergeCells count="92">
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E37:G38"/>
     <mergeCell ref="B38:D38"/>
@@ -3215,44 +3200,59 @@
     <mergeCell ref="B35:D36"/>
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Documents\git\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Projects\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EA6226-D8C0-446D-B10E-7C23D1B13B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF9CCEC-C4C8-43FF-80CE-F041EA00CEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">                                                                                                                  </t>
   </si>
@@ -74,18 +74,9 @@
     <t>m² aprox.</t>
   </si>
   <si>
-    <t>Medidas:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ubicación: </t>
-  </si>
-  <si>
     <t>Telefono:</t>
   </si>
   <si>
-    <t>DNI Nº:</t>
-  </si>
-  <si>
     <t>Fecha:</t>
   </si>
   <si>
@@ -104,60 +95,30 @@
     <t>1.4 Tasación de Inmueble</t>
   </si>
   <si>
-    <t>A. Desarrollo de Planos</t>
-  </si>
-  <si>
     <t>A.1 Anteproyecto (Hasta 3 Diseños)</t>
   </si>
   <si>
-    <t>A,11 Ubicación Coordenadas PSAD56 o WGS84</t>
-  </si>
-  <si>
     <t>A.2 Arquitectura-Distribución</t>
   </si>
   <si>
-    <t>A.12 Ubicación Coordenadas PSAD56 o WGS84</t>
-  </si>
-  <si>
     <t>A.3 Cortes Y elevaciones</t>
   </si>
   <si>
-    <t>A.13 Plano Perimetrico - Independización</t>
-  </si>
-  <si>
     <t xml:space="preserve">A.4 Estructuras Cimentación </t>
   </si>
   <si>
-    <t xml:space="preserve">A.14 Plano Ubicación </t>
-  </si>
-  <si>
     <t>A.5 Estructuras Techos</t>
   </si>
   <si>
-    <t>A.15 Cuadro tecnico</t>
-  </si>
-  <si>
-    <t>A.10 Ubicación y Localización</t>
-  </si>
-  <si>
-    <t>A.16 Plano Distribución</t>
-  </si>
-  <si>
     <t>B.  Elaboración de Documentos del Expediente Solicitado</t>
   </si>
   <si>
     <t>B.1 Lectura Titulo SUNARP (si fuera el caso)</t>
   </si>
   <si>
-    <t>B.15 Presupuesto de Obra</t>
-  </si>
-  <si>
     <t>B.2 Solicitud y Memoria Descriptiva SUNARP</t>
   </si>
   <si>
-    <t>B.16. Escrito notarial si fuese requerido</t>
-  </si>
-  <si>
     <t>B.3 Reglamento interno y junta de Propietarios (si fuera el caso)</t>
   </si>
   <si>
@@ -185,9 +146,6 @@
     <t>B.6 Constancia y Acta Extraordinaria (si fuera el caso)</t>
   </si>
   <si>
-    <t>B.22 Escrito de respuesta municipal</t>
-  </si>
-  <si>
     <t>B.7 Informe Tecnico de Verificación</t>
   </si>
   <si>
@@ -218,9 +176,6 @@
     <t>B.26 Solicitud municipal</t>
   </si>
   <si>
-    <t>B.13 Memoria(s) descriptiva(s)</t>
-  </si>
-  <si>
     <t>B.14 Sucesión Intestada</t>
   </si>
   <si>
@@ -308,9 +263,6 @@
     <t>Ing. Sanitario José Francisco Javier Zela Steban CIP: 130333</t>
   </si>
   <si>
-    <t>A la Aprobación de la Presente Proforma y Medición del Inmueble</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cuota 1 S/  </t>
   </si>
   <si>
@@ -339,6 +291,60 @@
   </si>
   <si>
     <t>Solicitante:</t>
+  </si>
+  <si>
+    <t>A.6 Ubicación y Localización</t>
+  </si>
+  <si>
+    <t>A.7 Ubicación Coordenadas WGS84</t>
+  </si>
+  <si>
+    <t>A.8 Ubicación Coordenadas PSAD56</t>
+  </si>
+  <si>
+    <t>A.10 Perimetrico - Subdivision</t>
+  </si>
+  <si>
+    <t>A.11 Perimetrico - Acumulacion</t>
+  </si>
+  <si>
+    <t>A.9 Plano Perimetrico - Independización</t>
+  </si>
+  <si>
+    <t>A.12 Evaluación Estructural de Inmueble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distrito: </t>
+  </si>
+  <si>
+    <t>N° Titulos:</t>
+  </si>
+  <si>
+    <t>A. Desarrollo de Planos del Expediente</t>
+  </si>
+  <si>
+    <t>B.16 Escrito notarial si fuese requerido</t>
+  </si>
+  <si>
+    <t>B.22 Audiencia con registrador SUNARP</t>
+  </si>
+  <si>
+    <t>B.27 Desistimiento de titulo en curso</t>
+  </si>
+  <si>
+    <t>B.28 Solicitud de tacha de titulo</t>
+  </si>
+  <si>
+    <t>B.13 Memoria descriptiva</t>
+  </si>
+  <si>
+    <t>A la Aprobación de la Proforma y Medición del Inmueble</t>
+  </si>
+  <si>
+    <t>DNI / RUC Nº:</t>
+  </si>
+  <si>
+    <t>B.15 Declaración Jurada Profesional</t>
   </si>
 </sst>
 </file>
@@ -348,7 +354,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-C0A]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,13 +455,6 @@
       <sz val="9"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="2" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -690,7 +689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -771,32 +770,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -833,13 +808,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -868,9 +855,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -896,15 +880,15 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -920,27 +904,27 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -956,35 +940,23 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1003,21 +975,9 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
@@ -1134,6 +1094,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
@@ -1146,11 +1118,35 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1190,14 +1186,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1215,7 +1203,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1959,9 +1947,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1999,7 +1987,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2105,7 +2093,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2247,7 +2235,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2260,7 +2248,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:H80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
@@ -2279,86 +2267,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="144" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
+      <c r="D4" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="145" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
+      <c r="D5" s="142" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="146" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="146"/>
-      <c r="F6" s="146"/>
+      <c r="D6" s="143" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="147" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
+      <c r="D7" s="144" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="148"/>
-      <c r="B8" s="148"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="148"/>
-      <c r="E8" s="148"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="148"/>
+      <c r="A8" s="145"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="145"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="143" t="s">
+      <c r="B9" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="143"/>
-      <c r="D9" s="143"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="143"/>
-      <c r="G9" s="143"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="143"/>
-      <c r="C10" s="143"/>
-      <c r="D10" s="143"/>
-      <c r="E10" s="143"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="143"/>
+      <c r="B10" s="140"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="131" t="s">
+      <c r="B11" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2367,29 +2355,29 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" s="45"/>
+        <v>82</v>
+      </c>
+      <c r="B14" s="39"/>
       <c r="C14" s="13" t="s">
         <v>9</v>
       </c>
@@ -2398,49 +2386,49 @@
         <v>10</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
+        <v>83</v>
+      </c>
+      <c r="B15" s="130"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
       <c r="F15" s="13" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="132"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
       <c r="F16" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="131"/>
+        <v>100</v>
+      </c>
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
       <c r="D17" s="18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E17" s="19">
         <f ca="1">TODAY()</f>
-        <v>46071</v>
+        <v>46076</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2448,514 +2436,518 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="133"/>
-      <c r="C18" s="133"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
-      <c r="B19" s="134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="135"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="137"/>
+      <c r="B19" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="134"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="136"/>
       <c r="H19" s="22"/>
     </row>
     <row r="20" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="138" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="139"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="141" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="141"/>
-      <c r="G20" s="142"/>
+      <c r="B20" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="138"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="128"/>
+      <c r="G20" s="129"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="126" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="127" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="127"/>
-      <c r="G21" s="128"/>
+      <c r="B21" s="119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="120"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="120" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="120"/>
+      <c r="G21" s="121"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="130"/>
+      <c r="B22" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="126"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="126" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="127"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="126" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="127"/>
-      <c r="G23" s="128"/>
+      <c r="B23" s="119" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="120"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="128"/>
+      <c r="G23" s="129"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="126" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="127"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="126" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="127"/>
-      <c r="G24" s="128"/>
+      <c r="B24" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="120"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="119" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="120"/>
+      <c r="G24" s="121"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="126" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="66"/>
-      <c r="G25" s="67"/>
+      <c r="B25" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="120"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="62"/>
+      <c r="G25" s="63"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="126" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="127"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="126" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="127"/>
-      <c r="G26" s="128"/>
+      <c r="B26" s="119" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="120"/>
+      <c r="D26" s="121"/>
+      <c r="E26" s="119" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="120"/>
+      <c r="G26" s="121"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="82" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="83"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="126" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="127"/>
-      <c r="G27" s="128"/>
+      <c r="B27" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="122" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="123"/>
+      <c r="G27" s="124"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="109" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="110"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="113"/>
-      <c r="G28" s="114"/>
+      <c r="B28" s="99" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="102" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="103"/>
+      <c r="G28" s="104"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="116"/>
+      <c r="B29" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="106"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="117" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="31"/>
-      <c r="G30" s="32"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="108"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="116" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="117"/>
+      <c r="G30" s="118"/>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="98"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="27"/>
-      <c r="G31" s="28"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="88"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="120" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
+      <c r="A32" s="27"/>
+      <c r="B32" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="111"/>
+      <c r="D32" s="112"/>
+      <c r="E32" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="41"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="120"/>
-      <c r="C33" s="121"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="F33" s="83"/>
-      <c r="G33" s="84"/>
+      <c r="B33" s="110"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="83"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="83"/>
-      <c r="G34" s="84"/>
+      <c r="B34" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="41"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="41"/>
+      <c r="G34" s="42"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="123" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="124"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="82" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35" s="83"/>
-      <c r="G35" s="84"/>
+      <c r="B35" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="114"/>
+      <c r="D35" s="115"/>
+      <c r="E35" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="41"/>
+      <c r="G35" s="42"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="123"/>
-      <c r="C36" s="124"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="97" t="s">
-        <v>46</v>
-      </c>
-      <c r="F36" s="98"/>
-      <c r="G36" s="99"/>
+      <c r="B36" s="113"/>
+      <c r="C36" s="114"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="87" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="88"/>
+      <c r="G36" s="89"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="82" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="83"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="106" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37" s="107"/>
-      <c r="G37" s="108"/>
+      <c r="B37" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="96" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="97"/>
+      <c r="G37" s="98"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="97" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="98"/>
-      <c r="D38" s="99"/>
-      <c r="E38" s="106"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="108"/>
+      <c r="B38" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="88"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="96"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="98"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="97" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="98"/>
-      <c r="D39" s="99"/>
-      <c r="E39" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="F39" s="101"/>
-      <c r="G39" s="102"/>
+      <c r="B39" s="87" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="88"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" s="91"/>
+      <c r="G39" s="92"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="97" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="98"/>
-      <c r="D40" s="99"/>
-      <c r="E40" s="103" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40" s="104"/>
-      <c r="G40" s="105"/>
+      <c r="B40" s="87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="88"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="93" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" s="94"/>
+      <c r="G40" s="95"/>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="98"/>
-      <c r="D41" s="99"/>
-      <c r="E41" s="106" t="s">
-        <v>55</v>
-      </c>
-      <c r="F41" s="107"/>
-      <c r="G41" s="108"/>
+      <c r="B41" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="88"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="96" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" s="97"/>
+      <c r="G41" s="98"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="97" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" s="98"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="107"/>
-      <c r="G42" s="108"/>
+      <c r="B42" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="88"/>
+      <c r="D42" s="89"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="97"/>
+      <c r="G42" s="98"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="82" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="83"/>
-      <c r="D43" s="84"/>
-      <c r="E43" s="85" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="86"/>
-      <c r="G43" s="87"/>
+      <c r="B43" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="41"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="79"/>
+      <c r="G43" s="80"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="82" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" s="83"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="90"/>
+      <c r="B44" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" s="82"/>
+      <c r="G44" s="83"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="91" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="94"/>
-      <c r="F45" s="95"/>
-      <c r="G45" s="96"/>
+      <c r="B45" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="41"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="84" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="85"/>
+      <c r="G45" s="86"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="61"/>
+      <c r="B46" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="57"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="62" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" s="63"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="66"/>
-      <c r="G47" s="67"/>
+      <c r="B47" s="58" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="59"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" s="62"/>
+      <c r="G47" s="63"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="68" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="69"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="68" t="s">
-        <v>65</v>
-      </c>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="B48" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="65"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" s="65"/>
+      <c r="G48" s="66"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="68" t="s">
-        <v>66</v>
-      </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="71" t="s">
-        <v>67</v>
-      </c>
-      <c r="F49" s="72"/>
-      <c r="G49" s="73"/>
+      <c r="B49" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="65"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" s="68"/>
+      <c r="G49" s="69"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="75"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="79"/>
+      <c r="B50" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="80"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="80"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="76"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10"/>
-      <c r="B52" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
+      <c r="B52" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="77"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="77"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="57"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="57"/>
-      <c r="E54" s="57"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
-      <c r="B56" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="B56" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
       <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
-      <c r="B57" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="35">
+      <c r="B57" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="48"/>
+      <c r="D57" s="29">
         <v>6</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
@@ -2963,180 +2955,180 @@
     </row>
     <row r="58" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
-      <c r="B58" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="C58" s="50"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
+      <c r="B58" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="47"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
       <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
-      <c r="B59" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="C59" s="52"/>
-      <c r="D59" s="37">
+      <c r="B59" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="49"/>
+      <c r="D59" s="31">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="53"/>
+      <c r="E59" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="F59" s="50"/>
       <c r="G59" s="20"/>
       <c r="H59" s="22"/>
     </row>
     <row r="60" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
-      <c r="B60" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C60" s="50"/>
-      <c r="D60" s="50"/>
-      <c r="E60" s="50"/>
-      <c r="F60" s="50"/>
-      <c r="G60" s="50"/>
+      <c r="B60" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="47"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47"/>
       <c r="H60" s="22"/>
     </row>
     <row r="61" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22"/>
-      <c r="B61" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="38"/>
-      <c r="D61" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="55"/>
-      <c r="F61" s="55"/>
-      <c r="G61" s="39">
+      <c r="B61" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="32"/>
+      <c r="D61" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E61" s="51"/>
+      <c r="F61" s="51"/>
+      <c r="G61" s="33">
         <f ca="1">E$17</f>
-        <v>46071</v>
+        <v>46076</v>
       </c>
       <c r="H61" s="22"/>
     </row>
     <row r="62" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="22"/>
-      <c r="B62" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" s="40"/>
-      <c r="D62" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62" s="55"/>
-      <c r="F62" s="55"/>
-      <c r="G62" s="39">
+      <c r="B62" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" s="34"/>
+      <c r="D62" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" s="51"/>
+      <c r="F62" s="51"/>
+      <c r="G62" s="33">
         <f ca="1">E$17+8</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="H62" s="22"/>
     </row>
     <row r="63" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="22"/>
-      <c r="B63" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" s="40"/>
-      <c r="D63" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" s="55"/>
-      <c r="F63" s="55"/>
-      <c r="G63" s="39">
+      <c r="B63" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" s="34"/>
+      <c r="D63" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" s="51"/>
+      <c r="F63" s="51"/>
+      <c r="G63" s="33">
         <f ca="1">E$17+35</f>
-        <v>46106</v>
-      </c>
-      <c r="H63" s="41" t="s">
-        <v>79</v>
+        <v>46111</v>
+      </c>
+      <c r="H63" s="35" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C64" s="56"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="56"/>
-      <c r="F64" s="56"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="42"/>
+      <c r="B64" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="52"/>
+      <c r="D64" s="52"/>
+      <c r="E64" s="52"/>
+      <c r="F64" s="52"/>
+      <c r="G64" s="52"/>
+      <c r="H64" s="36"/>
     </row>
     <row r="65" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
+      <c r="A65" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
+      <c r="B66" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
+      <c r="B67" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="44"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C68" s="47"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
+      <c r="B68" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
+      <c r="B69" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="44"/>
-      <c r="C70" s="44"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
-      <c r="H70" s="44"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
     </row>
     <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3148,12 +3140,14 @@
     <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="B31:D32 B44:B45 C43:D44" name="Rango2"/>
-    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="B17:C17 E17 G15 G16:H16 D14 B14 B13:H13 B23:D23 B21:D21 E20:G22 B25:D27 B49:D49 B43 C45:D45 C42:D42 F32:G36 F31 F30:G30 E30:E36" name="Rango1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="B31:D32" name="Rango2"/>
+    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="B17:C17 E17 G15 G16:H16 D14 B14 B13:H13 B23:D23 B21:D21 E20:G22 B25:D27 B49:D49 C42:D42" name="Rango1"/>
     <protectedRange algorithmName="SHA-512" hashValue="zUrWTGEZiJFMgzDqDTBlVt+5/9aQcTuJw4/Tg0qXKmOEBmnAPkc2PftdRKWEJAjo6Tejl/2GECle77oEWrFAIQ==" saltValue="IwcVdvVtxL7J72Vc6oLNHQ==" spinCount="100000" sqref="E51:G51" name="Rango1_6"/>
-    <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2"/>
+    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="F32:G36 F31 F30:G30 E30:E36" name="Rango1_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2_1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="B43 C45:D45" name="Rango1_2"/>
   </protectedRanges>
-  <mergeCells count="92">
+  <mergeCells count="95">
     <mergeCell ref="B9:G10"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D5:F5"/>
@@ -3200,6 +3194,7 @@
     <mergeCell ref="B35:D36"/>
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E30:G30"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="B40:D40"/>
@@ -3213,6 +3208,7 @@
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B64:G64"/>
     <mergeCell ref="B54:G54"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="B47:D47"/>
@@ -3226,18 +3222,13 @@
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="C52:G52"/>
     <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="B60:G60"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="D62:F62"/>
     <mergeCell ref="D63:F63"/>
-    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="F69:G69"/>
     <mergeCell ref="B66:E66"/>
@@ -3246,6 +3237,12 @@
     <mergeCell ref="F67:H67"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>

--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Projects\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Documents\git\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF9CCEC-C4C8-43FF-80CE-F041EA00CEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8470154A-26B5-4E09-B960-14F311A9816F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -738,10 +738,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -815,54 +811,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -872,92 +890,180 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -978,232 +1084,126 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1947,9 +1947,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1987,7 +1987,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2093,7 +2093,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2235,7 +2235,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2248,7 +2248,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:H80"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
@@ -2267,86 +2267,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="141" t="s">
+      <c r="D4" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="142" t="s">
+      <c r="D5" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="143" t="s">
+      <c r="D6" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="143"/>
-      <c r="F6" s="143"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="144" t="s">
+      <c r="D7" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="144"/>
-      <c r="F7" s="144"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="145"/>
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="145"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="145"/>
-      <c r="H8" s="145"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="140" t="s">
+      <c r="B9" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="140"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="140"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="140"/>
-      <c r="C10" s="140"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2355,29 +2355,29 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="130"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="39"/>
+      <c r="B14" s="38"/>
       <c r="C14" s="13" t="s">
         <v>9</v>
       </c>
@@ -2388,45 +2388,45 @@
       <c r="F14" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="16"/>
+      <c r="G14" s="145"/>
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="130"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
       <c r="F15" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="16"/>
+      <c r="G15" s="145"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="131"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="F16" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="17"/>
+      <c r="G16" s="16"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="18" t="s">
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="18">
         <f ca="1">TODAY()</f>
         <v>46076</v>
       </c>
@@ -2435,700 +2435,700 @@
       <c r="H17" s="15"/>
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="132"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="20"/>
-    </row>
-    <row r="19" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="133" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="134"/>
-      <c r="D19" s="135"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="136"/>
-      <c r="H19" s="22"/>
-    </row>
-    <row r="20" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="21"/>
+    </row>
+    <row r="20" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="137" t="s">
+      <c r="B20" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="138"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="128" t="s">
+      <c r="C20" s="56"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="128"/>
-      <c r="G20" s="129"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="59"/>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="120"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="120" t="s">
+      <c r="C21" s="46"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="120"/>
-      <c r="G21" s="121"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="47"/>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="126"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="63"/>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="119" t="s">
+      <c r="B23" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="120"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="127" t="s">
+      <c r="C23" s="46"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="128"/>
-      <c r="G23" s="129"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="59"/>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="120"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="119" t="s">
+      <c r="C24" s="46"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="120"/>
-      <c r="G24" s="121"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="47"/>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="119" t="s">
+    <row r="25" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="23"/>
+      <c r="B25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="120"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="61" t="s">
+      <c r="C25" s="46"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="62"/>
-      <c r="G25" s="63"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="67"/>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="119" t="s">
+    <row r="26" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+      <c r="B26" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="120"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="119" t="s">
+      <c r="C26" s="46"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="120"/>
-      <c r="G26" s="121"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="47"/>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="40" t="s">
+    <row r="27" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+      <c r="B27" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="122" t="s">
+      <c r="C27" s="69"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="123"/>
-      <c r="G27" s="124"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="73"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="99" t="s">
+    <row r="28" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+      <c r="B28" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="100"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="102" t="s">
+      <c r="C28" s="81"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="103"/>
-      <c r="G28" s="104"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="85"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="54" t="s">
+    <row r="29" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+      <c r="B29" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="106"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="87"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="107" t="s">
+    <row r="30" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25"/>
+      <c r="B30" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="108"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="116" t="s">
+      <c r="C30" s="89"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="117"/>
-      <c r="G30" s="118"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="99"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26"/>
-      <c r="B31" s="87" t="s">
+    <row r="31" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25"/>
+      <c r="B31" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="88"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="40" t="s">
+      <c r="C31" s="78"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="F31" s="41"/>
-      <c r="G31" s="42"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="B32" s="110" t="s">
+    <row r="32" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="26"/>
+      <c r="B32" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="111"/>
-      <c r="D32" s="112"/>
-      <c r="E32" s="40" t="s">
+      <c r="C32" s="92"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="41"/>
-      <c r="G32" s="42"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="110"/>
-      <c r="C33" s="111"/>
-      <c r="D33" s="112"/>
-      <c r="E33" s="40" t="s">
+      <c r="B33" s="91"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="41"/>
-      <c r="G33" s="42"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="40" t="s">
+      <c r="C34" s="69"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="41"/>
-      <c r="G34" s="42"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="113" t="s">
+      <c r="B35" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="114"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="40" t="s">
+      <c r="C35" s="95"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="41"/>
-      <c r="G35" s="42"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="70"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="113"/>
-      <c r="C36" s="114"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="87" t="s">
+      <c r="B36" s="94"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="F36" s="88"/>
-      <c r="G36" s="89"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="79"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="41"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="96" t="s">
+      <c r="C37" s="69"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="97"/>
-      <c r="G37" s="98"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="76"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="87" t="s">
+      <c r="B38" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="98"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="76"/>
       <c r="H38" s="10"/>
     </row>
-    <row r="39" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="88"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="90" t="s">
+      <c r="C39" s="78"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="91"/>
-      <c r="G39" s="92"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="102"/>
       <c r="H39" s="10"/>
     </row>
-    <row r="40" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="87" t="s">
+      <c r="B40" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="88"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="93" t="s">
+      <c r="C40" s="78"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="F40" s="94"/>
-      <c r="G40" s="95"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="105"/>
       <c r="H40" s="10"/>
     </row>
-    <row r="41" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="87" t="s">
+      <c r="B41" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="88"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="96" t="s">
+      <c r="C41" s="78"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="97"/>
-      <c r="G41" s="98"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="76"/>
       <c r="H41" s="10"/>
     </row>
-    <row r="42" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="87" t="s">
+      <c r="B42" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="88"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="96"/>
-      <c r="F42" s="97"/>
-      <c r="G42" s="98"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="76"/>
       <c r="H42" s="10"/>
     </row>
-    <row r="43" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="40" t="s">
+      <c r="B43" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="78" t="s">
+      <c r="C43" s="69"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="79"/>
-      <c r="G43" s="80"/>
+      <c r="F43" s="107"/>
+      <c r="G43" s="108"/>
       <c r="H43" s="10"/>
     </row>
-    <row r="44" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="81" t="s">
+      <c r="C44" s="69"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="F44" s="82"/>
-      <c r="G44" s="83"/>
+      <c r="F44" s="110"/>
+      <c r="G44" s="111"/>
       <c r="H44" s="10"/>
     </row>
-    <row r="45" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="40" t="s">
+      <c r="B45" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="41"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="84" t="s">
+      <c r="C45" s="69"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="112" t="s">
         <v>97</v>
       </c>
-      <c r="F45" s="85"/>
-      <c r="G45" s="86"/>
+      <c r="F45" s="113"/>
+      <c r="G45" s="114"/>
       <c r="H45" s="10"/>
     </row>
-    <row r="46" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="54" t="s">
+    <row r="46" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="57"/>
+      <c r="C46" s="61"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="118"/>
       <c r="H46" s="10"/>
     </row>
-    <row r="47" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="58" t="s">
+      <c r="B47" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="59"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="61" t="s">
+      <c r="C47" s="120"/>
+      <c r="D47" s="121"/>
+      <c r="E47" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="62"/>
-      <c r="G47" s="63"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="67"/>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="64" t="s">
+      <c r="B48" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="65"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="64" t="s">
+      <c r="C48" s="123"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="F48" s="65"/>
-      <c r="G48" s="66"/>
+      <c r="F48" s="123"/>
+      <c r="G48" s="124"/>
       <c r="H48" s="10"/>
     </row>
-    <row r="49" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="64" t="s">
+      <c r="B49" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="65"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="67" t="s">
+      <c r="C49" s="123"/>
+      <c r="D49" s="124"/>
+      <c r="E49" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="F49" s="68"/>
-      <c r="G49" s="69"/>
+      <c r="F49" s="126"/>
+      <c r="G49" s="127"/>
       <c r="H49" s="10"/>
     </row>
-    <row r="50" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="70" t="s">
+      <c r="B50" s="128" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="71"/>
-      <c r="D50" s="72"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="C50" s="129"/>
+      <c r="D50" s="130"/>
+      <c r="E50" s="131"/>
+      <c r="F50" s="132"/>
+      <c r="G50" s="133"/>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="76"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="76"/>
+      <c r="B51" s="134"/>
+      <c r="C51" s="134"/>
+      <c r="D51" s="134"/>
+      <c r="E51" s="134"/>
+      <c r="F51" s="134"/>
+      <c r="G51" s="134"/>
       <c r="H51" s="10"/>
     </row>
-    <row r="52" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10"/>
-      <c r="B52" s="28" t="s">
+      <c r="B52" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="77"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="77"/>
-      <c r="G52" s="77"/>
+      <c r="C52" s="135"/>
+      <c r="D52" s="135"/>
+      <c r="E52" s="135"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
       <c r="H52" s="10"/>
     </row>
-    <row r="53" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="53"/>
-      <c r="E53" s="53"/>
-      <c r="F53" s="53"/>
-      <c r="G53" s="53"/>
+      <c r="B53" s="116"/>
+      <c r="C53" s="116"/>
+      <c r="D53" s="116"/>
+      <c r="E53" s="116"/>
+      <c r="F53" s="116"/>
+      <c r="G53" s="116"/>
       <c r="H53" s="10"/>
     </row>
-    <row r="54" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
-      <c r="D54" s="53"/>
-      <c r="E54" s="53"/>
-      <c r="F54" s="53"/>
-      <c r="G54" s="53"/>
+      <c r="B54" s="116"/>
+      <c r="C54" s="116"/>
+      <c r="D54" s="116"/>
+      <c r="E54" s="116"/>
+      <c r="F54" s="116"/>
+      <c r="G54" s="116"/>
       <c r="H54" s="10"/>
     </row>
-    <row r="55" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
+      <c r="B55" s="142"/>
+      <c r="C55" s="142"/>
+      <c r="D55" s="142"/>
+      <c r="E55" s="142"/>
+      <c r="F55" s="142"/>
+      <c r="G55" s="142"/>
       <c r="H55" s="10"/>
     </row>
-    <row r="56" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="21"/>
-      <c r="B56" s="47" t="s">
+    <row r="56" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="20"/>
+      <c r="B56" s="137" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="47"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="47"/>
-      <c r="G56" s="47"/>
-      <c r="H56" s="22"/>
-    </row>
-    <row r="57" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="22"/>
-      <c r="B57" s="48" t="s">
+      <c r="C56" s="137"/>
+      <c r="D56" s="137"/>
+      <c r="E56" s="137"/>
+      <c r="F56" s="137"/>
+      <c r="G56" s="137"/>
+      <c r="H56" s="21"/>
+    </row>
+    <row r="57" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="21"/>
+      <c r="B57" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="48"/>
-      <c r="D57" s="29">
+      <c r="C57" s="143"/>
+      <c r="D57" s="28">
         <v>6</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="22"/>
-    </row>
-    <row r="58" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="21"/>
-      <c r="B58" s="47" t="s">
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="21"/>
+    </row>
+    <row r="58" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="20"/>
+      <c r="B58" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="22"/>
-    </row>
-    <row r="59" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="22"/>
-      <c r="B59" s="49" t="s">
+      <c r="C58" s="137"/>
+      <c r="D58" s="137"/>
+      <c r="E58" s="137"/>
+      <c r="F58" s="137"/>
+      <c r="G58" s="137"/>
+      <c r="H58" s="21"/>
+    </row>
+    <row r="59" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="21"/>
+      <c r="B59" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="49"/>
-      <c r="D59" s="31">
+      <c r="C59" s="144"/>
+      <c r="D59" s="30">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="50" t="s">
+      <c r="E59" s="136" t="s">
         <v>60</v>
       </c>
-      <c r="F59" s="50"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="22"/>
-    </row>
-    <row r="60" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="21"/>
-      <c r="B60" s="47" t="s">
+      <c r="F59" s="136"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="21"/>
+    </row>
+    <row r="60" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="20"/>
+      <c r="B60" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="47"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="22"/>
-    </row>
-    <row r="61" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="22"/>
-      <c r="B61" s="30" t="s">
+      <c r="C60" s="137"/>
+      <c r="D60" s="137"/>
+      <c r="E60" s="137"/>
+      <c r="F60" s="137"/>
+      <c r="G60" s="137"/>
+      <c r="H60" s="21"/>
+    </row>
+    <row r="61" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="21"/>
+      <c r="B61" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="C61" s="32"/>
-      <c r="D61" s="51" t="s">
+      <c r="C61" s="31"/>
+      <c r="D61" s="138" t="s">
         <v>99</v>
       </c>
-      <c r="E61" s="51"/>
-      <c r="F61" s="51"/>
-      <c r="G61" s="33">
+      <c r="E61" s="138"/>
+      <c r="F61" s="138"/>
+      <c r="G61" s="32">
         <f ca="1">E$17</f>
         <v>46076</v>
       </c>
-      <c r="H61" s="22"/>
-    </row>
-    <row r="62" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="22"/>
-      <c r="B62" s="30" t="s">
+      <c r="H61" s="21"/>
+    </row>
+    <row r="62" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="21"/>
+      <c r="B62" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C62" s="34"/>
-      <c r="D62" s="51" t="s">
+      <c r="C62" s="33"/>
+      <c r="D62" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="E62" s="51"/>
-      <c r="F62" s="51"/>
-      <c r="G62" s="33">
+      <c r="E62" s="138"/>
+      <c r="F62" s="138"/>
+      <c r="G62" s="32">
         <f ca="1">E$17+8</f>
         <v>46084</v>
       </c>
-      <c r="H62" s="22"/>
-    </row>
-    <row r="63" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="22"/>
-      <c r="B63" s="30" t="s">
+      <c r="H62" s="21"/>
+    </row>
+    <row r="63" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="21"/>
+      <c r="B63" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="C63" s="34"/>
-      <c r="D63" s="51" t="s">
+      <c r="C63" s="33"/>
+      <c r="D63" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="33">
+      <c r="E63" s="138"/>
+      <c r="F63" s="138"/>
+      <c r="G63" s="32">
         <f ca="1">E$17+35</f>
         <v>46111</v>
       </c>
-      <c r="H63" s="35" t="s">
+      <c r="H63" s="34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="52" t="s">
+      <c r="B64" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
-      <c r="H64" s="36"/>
-    </row>
-    <row r="65" spans="1:8" s="23" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="37" t="s">
+      <c r="C64" s="115"/>
+      <c r="D64" s="115"/>
+      <c r="E64" s="115"/>
+      <c r="F64" s="115"/>
+      <c r="G64" s="115"/>
+      <c r="H64" s="35"/>
+    </row>
+    <row r="65" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="B65" s="45" t="s">
+      <c r="B65" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
+      <c r="C65" s="141"/>
+      <c r="D65" s="141"/>
+      <c r="E65" s="141"/>
+      <c r="F65" s="141"/>
+      <c r="G65" s="141"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="43" t="s">
+      <c r="B66" s="139" t="s">
         <v>77</v>
       </c>
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43" t="s">
+      <c r="C66" s="139"/>
+      <c r="D66" s="139"/>
+      <c r="E66" s="139"/>
+      <c r="F66" s="139" t="s">
         <v>68</v>
       </c>
-      <c r="G66" s="43"/>
-      <c r="H66" s="43"/>
+      <c r="G66" s="139"/>
+      <c r="H66" s="139"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="44" t="s">
+      <c r="B67" s="140" t="s">
         <v>69</v>
       </c>
-      <c r="C67" s="44"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="43" t="s">
+      <c r="C67" s="140"/>
+      <c r="D67" s="140"/>
+      <c r="E67" s="140"/>
+      <c r="F67" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="G67" s="43"/>
-      <c r="H67" s="43"/>
+      <c r="G67" s="139"/>
+      <c r="H67" s="139"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="44" t="s">
+      <c r="B68" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="44"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="43" t="s">
+      <c r="C68" s="140"/>
+      <c r="D68" s="140"/>
+      <c r="E68" s="140"/>
+      <c r="F68" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="G68" s="43"/>
-      <c r="H68" s="43"/>
+      <c r="G68" s="139"/>
+      <c r="H68" s="139"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="43" t="s">
+      <c r="B69" s="139" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="43"/>
+      <c r="C69" s="139"/>
+      <c r="D69" s="139"/>
+      <c r="E69" s="139"/>
+      <c r="F69" s="139"/>
+      <c r="G69" s="139"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="38"/>
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="37"/>
     </row>
     <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3148,37 +3148,54 @@
     <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="B43 C45:D45" name="Rango1_2"/>
   </protectedRanges>
   <mergeCells count="95">
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E37:G38"/>
     <mergeCell ref="B38:D38"/>
@@ -3195,54 +3212,37 @@
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>

--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Documents\git\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Projects\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8470154A-26B5-4E09-B960-14F311A9816F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E941C5A-5870-455E-A49E-4887C09F1721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -128,57 +128,24 @@
     <t>B.18 Carta de Seguridad de Obra</t>
   </si>
   <si>
-    <t>B.4 Formulario Registral Nº 2</t>
-  </si>
-  <si>
     <t>B.19 Carta de Responsabilidad de Obra</t>
   </si>
   <si>
-    <t>B.5 Modificación de Reglamento interno y junta de Propietarios (si fuera el caso)</t>
-  </si>
-  <si>
     <t>B.20 Escrito para respuesta de Notificacion Municpal</t>
   </si>
   <si>
     <t>B.21 Asesoria durante el proceso</t>
   </si>
   <si>
-    <t>B.6 Constancia y Acta Extraordinaria (si fuera el caso)</t>
-  </si>
-  <si>
-    <t>B.7 Informe Tecnico de Verificación</t>
-  </si>
-  <si>
-    <t>B.8 Declaracion Jurada</t>
-  </si>
-  <si>
     <t>B.23 Revisión de notificacion y normativa</t>
   </si>
   <si>
-    <t>B.9 Anexo Nº 1 SUNARP</t>
-  </si>
-  <si>
     <t>B.24 Verificación de código de multa</t>
   </si>
   <si>
-    <t>B.10 Anexo Nº 4 SUNARP</t>
-  </si>
-  <si>
     <t>B.25 Trámite municipal</t>
   </si>
   <si>
-    <t>B.11 Subsanacion de observaciones SUNARP (si fuera el caso)</t>
-  </si>
-  <si>
-    <t>B.12 FUE (Formulario Unico de Edifcaciones)</t>
-  </si>
-  <si>
-    <t>B.26 Solicitud municipal</t>
-  </si>
-  <si>
-    <t>B.14 Sucesión Intestada</t>
-  </si>
-  <si>
     <t>2.- ALCANCES: ENTREGA DE DOCUMENTOS FIRMADOS – PROFESIONALES VIGENTES</t>
   </si>
   <si>
@@ -335,9 +302,6 @@
     <t>B.28 Solicitud de tacha de titulo</t>
   </si>
   <si>
-    <t>B.13 Memoria descriptiva</t>
-  </si>
-  <si>
     <t>A la Aprobación de la Proforma y Medición del Inmueble</t>
   </si>
   <si>
@@ -345,6 +309,42 @@
   </si>
   <si>
     <t>B.15 Declaración Jurada Profesional</t>
+  </si>
+  <si>
+    <t>B.4 Formulario Registral Nº 1</t>
+  </si>
+  <si>
+    <t>B.5 Formulario Registral Nº 2</t>
+  </si>
+  <si>
+    <t>B.6 Modificación de Reglamento interno y junta de Propietarios (si fuera el caso)</t>
+  </si>
+  <si>
+    <t>B.7 Constancia y Acta Extraordinaria (si fuera el caso)</t>
+  </si>
+  <si>
+    <t>B.8 Informe Tecnico de Verificación</t>
+  </si>
+  <si>
+    <t>B.9 Declaracion Jurada</t>
+  </si>
+  <si>
+    <t>B.10 Anexo Nº 1 SUNARP</t>
+  </si>
+  <si>
+    <t>B.11 Anexo Nº 4 SUNARP</t>
+  </si>
+  <si>
+    <t>B.12 Subsanacion de observaciones SUNARP (si fuera el caso)</t>
+  </si>
+  <si>
+    <t>B.13 FUE (Formulario Unico de Edifcaciones)</t>
+  </si>
+  <si>
+    <t>B.14 Memoria descriptiva</t>
+  </si>
+  <si>
+    <t>B.26 Sucesión Intestada</t>
   </si>
 </sst>
 </file>
@@ -689,7 +689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -811,21 +811,319 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -834,6 +1132,38 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -874,336 +1204,27 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1947,9 +1968,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1987,7 +2008,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2093,7 +2114,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2235,7 +2256,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2248,7 +2269,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:H80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
@@ -2267,86 +2288,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="D4" s="143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
+      <c r="D5" s="144" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
+      <c r="D6" s="145" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
+      <c r="D7" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="146"/>
+      <c r="F7" s="146"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
+      <c r="A8" s="147"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="147"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="142"/>
+      <c r="E9" s="142"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="142"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
+      <c r="B10" s="142"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2355,27 +2376,27 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
+      <c r="B12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
+      <c r="B13" s="132"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B14" s="38"/>
       <c r="C14" s="13" t="s">
@@ -2386,31 +2407,31 @@
         <v>10</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="145"/>
+        <v>81</v>
+      </c>
+      <c r="G14" s="45"/>
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
+        <v>72</v>
+      </c>
+      <c r="B15" s="132"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
       <c r="F15" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" s="145"/>
+        <v>80</v>
+      </c>
+      <c r="G15" s="45"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
       <c r="F16" s="13" t="s">
         <v>11</v>
       </c>
@@ -2419,16 +2440,16 @@
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
+        <v>88</v>
+      </c>
+      <c r="B17" s="132"/>
+      <c r="C17" s="132"/>
       <c r="D17" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2436,518 +2457,518 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
+      <c r="B18" s="134"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
       <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="138"/>
       <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="58" t="s">
+      <c r="C20" s="140"/>
+      <c r="D20" s="141"/>
+      <c r="E20" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="58"/>
-      <c r="G20" s="59"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="131"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="46" t="s">
+      <c r="C21" s="122"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="123"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="63"/>
+      <c r="B22" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="127"/>
+      <c r="G22" s="128"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="58"/>
-      <c r="G23" s="59"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="129" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="130"/>
+      <c r="G23" s="131"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="122"/>
+      <c r="G24" s="123"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="66"/>
-      <c r="G25" s="67"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="67"/>
+      <c r="G25" s="68"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24"/>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="121" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="122"/>
+      <c r="G26" s="123"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="71" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="72"/>
-      <c r="G27" s="73"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="124" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="125"/>
+      <c r="G27" s="126"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
-      <c r="B28" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="81"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="84"/>
-      <c r="G28" s="85"/>
+      <c r="B28" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="103"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="105" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="106"/>
+      <c r="G28" s="107"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="87"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="109"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
-      <c r="B30" s="88" t="s">
+      <c r="B30" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="89"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="F30" s="98"/>
-      <c r="G30" s="99"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="112"/>
+      <c r="E30" s="118" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="119"/>
+      <c r="G30" s="120"/>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56"/>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26"/>
-      <c r="B32" s="91" t="s">
+      <c r="B32" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="92"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="68" t="s">
+      <c r="C32" s="114"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="91"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="68" t="s">
+      <c r="B33" s="113"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="55"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="56"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="95"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="68" t="s">
-        <v>32</v>
-      </c>
-      <c r="F35" s="69"/>
-      <c r="G35" s="70"/>
+      <c r="B35" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="55"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="55"/>
+      <c r="G35" s="56"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="F36" s="78"/>
-      <c r="G36" s="79"/>
+      <c r="B36" s="116" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="148"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="90" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="91"/>
+      <c r="G36" s="92"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="68" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="69"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="75"/>
-      <c r="G37" s="76"/>
+      <c r="B37" s="116"/>
+      <c r="C37" s="148"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="99" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="100"/>
+      <c r="G37" s="101"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
-      <c r="B38" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="78"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="76"/>
+      <c r="B38" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="40"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="101"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
-      <c r="B39" s="77" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="78"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="100" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39" s="101"/>
-      <c r="G39" s="102"/>
+      <c r="B39" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="43"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="93" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" s="94"/>
+      <c r="G39" s="95"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
-      <c r="B40" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="103" t="s">
-        <v>39</v>
-      </c>
-      <c r="F40" s="104"/>
-      <c r="G40" s="105"/>
+      <c r="B40" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="43"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="97"/>
+      <c r="G40" s="98"/>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
-      <c r="B41" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="78"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" s="75"/>
-      <c r="G41" s="76"/>
+      <c r="B41" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="43"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="101"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
-      <c r="B42" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="78"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="76"/>
+      <c r="B42" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="43"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="99"/>
+      <c r="F42" s="100"/>
+      <c r="G42" s="101"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
-      <c r="B43" s="68" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="69"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="106" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="107"/>
-      <c r="G43" s="108"/>
+      <c r="B43" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="43"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" s="55"/>
+      <c r="G43" s="56"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
-      <c r="B44" s="68" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" s="69"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="109" t="s">
-        <v>96</v>
-      </c>
-      <c r="F44" s="110"/>
-      <c r="G44" s="111"/>
+      <c r="B44" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="40"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" s="85"/>
+      <c r="G44" s="86"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
-      <c r="B45" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="112" t="s">
-        <v>97</v>
-      </c>
-      <c r="F45" s="113"/>
-      <c r="G45" s="114"/>
+      <c r="B45" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="88"/>
+      <c r="G45" s="89"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="117"/>
-      <c r="F46" s="117"/>
-      <c r="G46" s="118"/>
+      <c r="B46" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="62"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="119" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="120"/>
-      <c r="D47" s="121"/>
-      <c r="E47" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" s="66"/>
-      <c r="G47" s="67"/>
+      <c r="B47" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" s="67"/>
+      <c r="G47" s="68"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="122" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="123"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="122" t="s">
-        <v>50</v>
-      </c>
-      <c r="F48" s="123"/>
-      <c r="G48" s="124"/>
+      <c r="B48" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="70"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="F48" s="70"/>
+      <c r="G48" s="71"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="122" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="123"/>
-      <c r="D49" s="124"/>
-      <c r="E49" s="125" t="s">
-        <v>52</v>
-      </c>
-      <c r="F49" s="126"/>
-      <c r="G49" s="127"/>
+      <c r="B49" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="70"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="72" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" s="73"/>
+      <c r="G49" s="74"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="128" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="129"/>
-      <c r="D50" s="130"/>
-      <c r="E50" s="131"/>
-      <c r="F50" s="132"/>
-      <c r="G50" s="133"/>
+      <c r="B50" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="76"/>
+      <c r="D50" s="77"/>
+      <c r="E50" s="78"/>
+      <c r="F50" s="79"/>
+      <c r="G50" s="80"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="134"/>
-      <c r="C51" s="134"/>
-      <c r="D51" s="134"/>
-      <c r="E51" s="134"/>
-      <c r="F51" s="134"/>
-      <c r="G51" s="134"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10"/>
       <c r="B52" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" s="135"/>
-      <c r="D52" s="135"/>
-      <c r="E52" s="135"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="135"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="82"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="116"/>
-      <c r="C53" s="116"/>
-      <c r="D53" s="116"/>
-      <c r="E53" s="116"/>
-      <c r="F53" s="116"/>
-      <c r="G53" s="116"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="116"/>
-      <c r="C54" s="116"/>
-      <c r="D54" s="116"/>
-      <c r="E54" s="116"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="116"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="142"/>
-      <c r="C55" s="142"/>
-      <c r="D55" s="142"/>
-      <c r="E55" s="142"/>
-      <c r="F55" s="142"/>
-      <c r="G55" s="142"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20"/>
-      <c r="B56" s="137" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="137"/>
-      <c r="D56" s="137"/>
-      <c r="E56" s="137"/>
-      <c r="F56" s="137"/>
-      <c r="G56" s="137"/>
+      <c r="B56" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
       <c r="H56" s="21"/>
     </row>
     <row r="57" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
-      <c r="B57" s="143" t="s">
-        <v>56</v>
-      </c>
-      <c r="C57" s="143"/>
+      <c r="B57" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="49"/>
       <c r="D57" s="28">
         <v>6</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F57" s="19"/>
       <c r="G57" s="19"/>
@@ -2955,171 +2976,171 @@
     </row>
     <row r="58" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20"/>
-      <c r="B58" s="137" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" s="137"/>
-      <c r="D58" s="137"/>
-      <c r="E58" s="137"/>
-      <c r="F58" s="137"/>
-      <c r="G58" s="137"/>
+      <c r="B58" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
       <c r="H58" s="21"/>
     </row>
     <row r="59" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
-      <c r="B59" s="144" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="144"/>
+      <c r="B59" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59" s="50"/>
       <c r="D59" s="30">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="136" t="s">
-        <v>60</v>
-      </c>
-      <c r="F59" s="136"/>
+      <c r="E59" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="F59" s="83"/>
       <c r="G59" s="19"/>
       <c r="H59" s="21"/>
     </row>
     <row r="60" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20"/>
-      <c r="B60" s="137" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="137"/>
-      <c r="D60" s="137"/>
-      <c r="E60" s="137"/>
-      <c r="F60" s="137"/>
-      <c r="G60" s="137"/>
+      <c r="B60" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
       <c r="H60" s="21"/>
     </row>
     <row r="61" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="29" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C61" s="31"/>
-      <c r="D61" s="138" t="s">
-        <v>99</v>
-      </c>
-      <c r="E61" s="138"/>
-      <c r="F61" s="138"/>
+      <c r="D61" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
       <c r="G61" s="32">
         <f ca="1">E$17</f>
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="H61" s="21"/>
     </row>
     <row r="62" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="29" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C62" s="33"/>
-      <c r="D62" s="138" t="s">
-        <v>62</v>
-      </c>
-      <c r="E62" s="138"/>
-      <c r="F62" s="138"/>
+      <c r="D62" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
       <c r="G62" s="32">
         <f ca="1">E$17+8</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="H62" s="21"/>
     </row>
     <row r="63" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="29" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C63" s="33"/>
-      <c r="D63" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="E63" s="138"/>
-      <c r="F63" s="138"/>
+      <c r="D63" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
       <c r="G63" s="32">
         <f ca="1">E$17+35</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="H63" s="34" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="115" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" s="115"/>
-      <c r="D64" s="115"/>
-      <c r="E64" s="115"/>
-      <c r="F64" s="115"/>
-      <c r="G64" s="115"/>
+      <c r="B64" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
       <c r="H64" s="35"/>
     </row>
     <row r="65" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
+    </row>
+    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="B65" s="141" t="s">
-        <v>67</v>
-      </c>
-      <c r="C65" s="141"/>
-      <c r="D65" s="141"/>
-      <c r="E65" s="141"/>
-      <c r="F65" s="141"/>
-      <c r="G65" s="141"/>
-    </row>
-    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="139" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" s="139"/>
-      <c r="D66" s="139"/>
-      <c r="E66" s="139"/>
-      <c r="F66" s="139" t="s">
-        <v>68</v>
-      </c>
-      <c r="G66" s="139"/>
-      <c r="H66" s="139"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
+      <c r="F66" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" s="51"/>
+      <c r="H66" s="51"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="140" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" s="140"/>
-      <c r="D67" s="140"/>
-      <c r="E67" s="140"/>
-      <c r="F67" s="139" t="s">
-        <v>70</v>
-      </c>
-      <c r="G67" s="139"/>
-      <c r="H67" s="139"/>
+      <c r="B67" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" s="52"/>
+      <c r="D67" s="52"/>
+      <c r="E67" s="52"/>
+      <c r="F67" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G67" s="51"/>
+      <c r="H67" s="51"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="140" t="s">
-        <v>71</v>
-      </c>
-      <c r="C68" s="140"/>
-      <c r="D68" s="140"/>
-      <c r="E68" s="140"/>
-      <c r="F68" s="139" t="s">
-        <v>72</v>
-      </c>
-      <c r="G68" s="139"/>
-      <c r="H68" s="139"/>
+      <c r="B68" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C68" s="52"/>
+      <c r="D68" s="52"/>
+      <c r="E68" s="52"/>
+      <c r="F68" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G68" s="51"/>
+      <c r="H68" s="51"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="139" t="s">
-        <v>73</v>
-      </c>
-      <c r="C69" s="139"/>
-      <c r="D69" s="139"/>
-      <c r="E69" s="139"/>
-      <c r="F69" s="139"/>
-      <c r="G69" s="139"/>
+      <c r="B69" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" s="51"/>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="37"/>
@@ -3141,30 +3162,65 @@
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="B31:D32" name="Rango2"/>
-    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="B17:C17 E17 G15 G16:H16 D14 B14 B13:H13 B23:D23 B21:D21 E20:G22 B25:D27 B49:D49 C42:D42" name="Rango1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="B17:C17 E17 G15 G16:H16 D14 B14 B13:H13 B23:D23 B21:D21 E20:G22 B25:D27 B49:D49 C43:D43" name="Rango1"/>
     <protectedRange algorithmName="SHA-512" hashValue="zUrWTGEZiJFMgzDqDTBlVt+5/9aQcTuJw4/Tg0qXKmOEBmnAPkc2PftdRKWEJAjo6Tejl/2GECle77oEWrFAIQ==" saltValue="IwcVdvVtxL7J72Vc6oLNHQ==" spinCount="100000" sqref="E51:G51" name="Rango1_6"/>
     <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="F32:G36 F31 F30:G30 E30:E36" name="Rango1_1"/>
     <protectedRange algorithmName="SHA-512" hashValue="1IwEtpPovyRjspz9ti3J5udl070IPZ9gDlGmM3ZH/lFyQlLVVL2qbaMds7kHvZZkPq7VvowLV2MqpNnf8owpjQ==" saltValue="SwYyjj//I75seGLqQP0hyQ==" spinCount="100000" sqref="E37:G38 E39" name="Rango2_2_1"/>
-    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="B43 C45:D45" name="Rango1_2"/>
+    <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="F43:G43" name="Rango1_3"/>
   </protectedRanges>
-  <mergeCells count="95">
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
+  <mergeCells count="87">
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D37"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="E45:G45"/>
     <mergeCell ref="E31:G31"/>
     <mergeCell ref="E32:G32"/>
     <mergeCell ref="B64:G64"/>
@@ -3181,68 +3237,25 @@
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="C52:G52"/>
     <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="B35:D36"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>

--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Projects\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Documents\git\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E941C5A-5870-455E-A49E-4887C09F1721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638B3DDA-5F30-4A34-8CB4-438551E91AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -839,6 +839,364 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -857,374 +1215,16 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1968,9 +1968,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2008,7 +2008,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2114,7 +2114,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2256,7 +2256,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2269,7 +2269,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:H80"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
@@ -2288,86 +2288,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="143" t="s">
+      <c r="D4" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="144" t="s">
+      <c r="D5" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="145" t="s">
+      <c r="D6" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="146" t="s">
+      <c r="D7" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="146"/>
-      <c r="F7" s="146"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="147"/>
-      <c r="B8" s="147"/>
-      <c r="C8" s="147"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="147"/>
-      <c r="H8" s="147"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="142" t="s">
+      <c r="B9" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="142"/>
-      <c r="E9" s="142"/>
-      <c r="F9" s="142"/>
-      <c r="G9" s="142"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="142"/>
-      <c r="C10" s="142"/>
-      <c r="D10" s="142"/>
-      <c r="E10" s="142"/>
-      <c r="F10" s="142"/>
-      <c r="G10" s="142"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="132" t="s">
+      <c r="B11" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2376,22 +2376,22 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="132"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="132"/>
-      <c r="G12" s="132"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2416,10 +2416,10 @@
       <c r="A15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="132"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
       <c r="F15" s="13" t="s">
         <v>80</v>
       </c>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
       <c r="F16" s="13" t="s">
         <v>11</v>
       </c>
@@ -2442,14 +2442,14 @@
       <c r="A17" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="132"/>
-      <c r="C17" s="132"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2457,268 +2457,268 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="134"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="134"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
       <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
-      <c r="B19" s="135" t="s">
+      <c r="B19" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="136"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="138"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
       <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="139" t="s">
+      <c r="B20" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="140"/>
-      <c r="D20" s="141"/>
-      <c r="E20" s="130" t="s">
+      <c r="C20" s="69"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="130"/>
-      <c r="G20" s="131"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="72"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="121" t="s">
+      <c r="B21" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="122"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="122" t="s">
+      <c r="C21" s="59"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="122"/>
-      <c r="G21" s="123"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="60"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="59" t="s">
+      <c r="B22" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="128"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="76"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="122"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="129" t="s">
+      <c r="C23" s="59"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="130"/>
-      <c r="G23" s="131"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="72"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="121" t="s">
+      <c r="B24" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="122"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="121" t="s">
+      <c r="C24" s="59"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="122"/>
-      <c r="G24" s="123"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="60"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="122"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="66" t="s">
+      <c r="C25" s="59"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="F25" s="67"/>
-      <c r="G25" s="68"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="80"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24"/>
-      <c r="B26" s="121" t="s">
+      <c r="B26" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="122"/>
-      <c r="D26" s="123"/>
-      <c r="E26" s="121" t="s">
+      <c r="C26" s="59"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="122"/>
-      <c r="G26" s="123"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="60"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="55"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="124" t="s">
+      <c r="C27" s="47"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="125"/>
-      <c r="G27" s="126"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="83"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
-      <c r="B28" s="102" t="s">
+      <c r="B28" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="103"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="105" t="s">
+      <c r="C28" s="88"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="106"/>
-      <c r="G28" s="107"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="92"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="109"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="94"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="111"/>
-      <c r="D30" s="112"/>
-      <c r="E30" s="118" t="s">
+      <c r="C30" s="96"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="119"/>
-      <c r="G30" s="120"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="106"/>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
-      <c r="B31" s="90" t="s">
+      <c r="B31" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="91"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="54" t="s">
+      <c r="C31" s="99"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="48"/>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26"/>
-      <c r="B32" s="113" t="s">
+      <c r="B32" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="114"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="54" t="s">
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="113"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="54" t="s">
+      <c r="B33" s="101"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="48"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="54" t="s">
+      <c r="C34" s="47"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="48"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="54" t="s">
+      <c r="C35" s="47"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="48"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="116" t="s">
+      <c r="B36" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="148"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="90" t="s">
+      <c r="C36" s="50"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="91"/>
-      <c r="G36" s="92"/>
+      <c r="F36" s="99"/>
+      <c r="G36" s="100"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="116"/>
-      <c r="C37" s="148"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="99" t="s">
+      <c r="B37" s="49"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="F37" s="100"/>
-      <c r="G37" s="101"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="86"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2728,9 +2728,9 @@
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="41"/>
-      <c r="E38" s="99"/>
-      <c r="F38" s="100"/>
-      <c r="G38" s="101"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="86"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2740,11 +2740,11 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44"/>
-      <c r="E39" s="93" t="s">
+      <c r="E39" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="F39" s="94"/>
-      <c r="G39" s="95"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="109"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2754,11 +2754,11 @@
       </c>
       <c r="C40" s="43"/>
       <c r="D40" s="44"/>
-      <c r="E40" s="96" t="s">
+      <c r="E40" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="97"/>
-      <c r="G40" s="98"/>
+      <c r="F40" s="111"/>
+      <c r="G40" s="112"/>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2768,11 +2768,11 @@
       </c>
       <c r="C41" s="43"/>
       <c r="D41" s="44"/>
-      <c r="E41" s="99" t="s">
+      <c r="E41" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="F41" s="100"/>
-      <c r="G41" s="101"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="86"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2782,9 +2782,9 @@
       </c>
       <c r="C42" s="43"/>
       <c r="D42" s="44"/>
-      <c r="E42" s="99"/>
-      <c r="F42" s="100"/>
-      <c r="G42" s="101"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="85"/>
+      <c r="G42" s="86"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2794,11 +2794,11 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44"/>
-      <c r="E43" s="54" t="s">
+      <c r="E43" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="F43" s="55"/>
-      <c r="G43" s="56"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="48"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C44" s="40"/>
       <c r="D44" s="41"/>
-      <c r="E44" s="84" t="s">
+      <c r="E44" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="F44" s="85"/>
-      <c r="G44" s="86"/>
+      <c r="F44" s="114"/>
+      <c r="G44" s="115"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2822,86 +2822,86 @@
       </c>
       <c r="C45" s="40"/>
       <c r="D45" s="41"/>
-      <c r="E45" s="87" t="s">
+      <c r="E45" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="88"/>
-      <c r="G45" s="89"/>
+      <c r="F45" s="117"/>
+      <c r="G45" s="118"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="60"/>
-      <c r="D46" s="60"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="62"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="122"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="66" t="s">
+      <c r="C47" s="124"/>
+      <c r="D47" s="125"/>
+      <c r="E47" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="F47" s="67"/>
-      <c r="G47" s="68"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="80"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="69" t="s">
+      <c r="C48" s="127"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="70"/>
-      <c r="G48" s="71"/>
+      <c r="F48" s="127"/>
+      <c r="G48" s="128"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="72" t="s">
+      <c r="C49" s="127"/>
+      <c r="D49" s="128"/>
+      <c r="E49" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="73"/>
-      <c r="G49" s="74"/>
+      <c r="F49" s="130"/>
+      <c r="G49" s="131"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="75" t="s">
+      <c r="B50" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="C50" s="76"/>
-      <c r="D50" s="77"/>
-      <c r="E50" s="78"/>
-      <c r="F50" s="79"/>
-      <c r="G50" s="80"/>
+      <c r="C50" s="133"/>
+      <c r="D50" s="134"/>
+      <c r="E50" s="135"/>
+      <c r="F50" s="136"/>
+      <c r="G50" s="137"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="81"/>
-      <c r="C51" s="81"/>
-      <c r="D51" s="81"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
+      <c r="B51" s="138"/>
+      <c r="C51" s="138"/>
+      <c r="D51" s="138"/>
+      <c r="E51" s="138"/>
+      <c r="F51" s="138"/>
+      <c r="G51" s="138"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2909,63 +2909,63 @@
       <c r="B52" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="82"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
+      <c r="C52" s="139"/>
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="139"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
+      <c r="B53" s="120"/>
+      <c r="C53" s="120"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="120"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
+      <c r="B54" s="120"/>
+      <c r="C54" s="120"/>
+      <c r="D54" s="120"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="120"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="47"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
+      <c r="B55" s="143"/>
+      <c r="C55" s="143"/>
+      <c r="D55" s="143"/>
+      <c r="E55" s="143"/>
+      <c r="F55" s="143"/>
+      <c r="G55" s="143"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20"/>
-      <c r="B56" s="48" t="s">
+      <c r="B56" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
+      <c r="C56" s="144"/>
+      <c r="D56" s="144"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="144"/>
       <c r="H56" s="21"/>
     </row>
     <row r="57" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
-      <c r="B57" s="49" t="s">
+      <c r="B57" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="49"/>
+      <c r="C57" s="145"/>
       <c r="D57" s="28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>46</v>
@@ -2976,43 +2976,43 @@
     </row>
     <row r="58" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20"/>
-      <c r="B58" s="48" t="s">
+      <c r="B58" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
+      <c r="C58" s="144"/>
+      <c r="D58" s="144"/>
+      <c r="E58" s="144"/>
+      <c r="F58" s="144"/>
+      <c r="G58" s="144"/>
       <c r="H58" s="21"/>
     </row>
     <row r="59" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
-      <c r="B59" s="50" t="s">
+      <c r="B59" s="146" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="50"/>
+      <c r="C59" s="146"/>
       <c r="D59" s="30">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="83" t="s">
+      <c r="E59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="F59" s="83"/>
+      <c r="F59" s="148"/>
       <c r="G59" s="19"/>
       <c r="H59" s="21"/>
     </row>
     <row r="60" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20"/>
-      <c r="B60" s="48" t="s">
+      <c r="B60" s="144" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
+      <c r="C60" s="144"/>
+      <c r="D60" s="144"/>
+      <c r="E60" s="144"/>
+      <c r="F60" s="144"/>
+      <c r="G60" s="144"/>
       <c r="H60" s="21"/>
     </row>
     <row r="61" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -3021,14 +3021,14 @@
         <v>63</v>
       </c>
       <c r="C61" s="31"/>
-      <c r="D61" s="53" t="s">
+      <c r="D61" s="147" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="53"/>
-      <c r="F61" s="53"/>
+      <c r="E61" s="147"/>
+      <c r="F61" s="147"/>
       <c r="G61" s="32">
         <f ca="1">E$17</f>
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H61" s="21"/>
     </row>
@@ -3038,14 +3038,14 @@
         <v>64</v>
       </c>
       <c r="C62" s="33"/>
-      <c r="D62" s="53" t="s">
+      <c r="D62" s="147" t="s">
         <v>51</v>
       </c>
-      <c r="E62" s="53"/>
-      <c r="F62" s="53"/>
+      <c r="E62" s="147"/>
+      <c r="F62" s="147"/>
       <c r="G62" s="32">
         <f ca="1">E$17+8</f>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H62" s="21"/>
     </row>
@@ -3055,14 +3055,14 @@
         <v>65</v>
       </c>
       <c r="C63" s="33"/>
-      <c r="D63" s="53" t="s">
+      <c r="D63" s="147" t="s">
         <v>52</v>
       </c>
-      <c r="E63" s="53"/>
-      <c r="F63" s="53"/>
+      <c r="E63" s="147"/>
+      <c r="F63" s="147"/>
       <c r="G63" s="32">
         <f ca="1">E$17+35</f>
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="H63" s="34" t="s">
         <v>53</v>
@@ -3070,77 +3070,77 @@
     </row>
     <row r="64" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="57" t="s">
+      <c r="B64" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
+      <c r="C64" s="119"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="119"/>
+      <c r="F64" s="119"/>
+      <c r="G64" s="119"/>
       <c r="H64" s="35"/>
     </row>
     <row r="65" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="46" t="s">
+      <c r="B65" s="142" t="s">
         <v>56</v>
       </c>
-      <c r="C65" s="46"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
+      <c r="C65" s="142"/>
+      <c r="D65" s="142"/>
+      <c r="E65" s="142"/>
+      <c r="F65" s="142"/>
+      <c r="G65" s="142"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="140" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="51"/>
-      <c r="D66" s="51"/>
-      <c r="E66" s="51"/>
-      <c r="F66" s="51" t="s">
+      <c r="C66" s="140"/>
+      <c r="D66" s="140"/>
+      <c r="E66" s="140"/>
+      <c r="F66" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="G66" s="51"/>
-      <c r="H66" s="51"/>
+      <c r="G66" s="140"/>
+      <c r="H66" s="140"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="52" t="s">
+      <c r="B67" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="C67" s="52"/>
-      <c r="D67" s="52"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="51" t="s">
+      <c r="C67" s="141"/>
+      <c r="D67" s="141"/>
+      <c r="E67" s="141"/>
+      <c r="F67" s="140" t="s">
         <v>59</v>
       </c>
-      <c r="G67" s="51"/>
-      <c r="H67" s="51"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="140"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="52" t="s">
+      <c r="B68" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="51" t="s">
+      <c r="C68" s="141"/>
+      <c r="D68" s="141"/>
+      <c r="E68" s="141"/>
+      <c r="F68" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="G68" s="51"/>
-      <c r="H68" s="51"/>
+      <c r="G68" s="140"/>
+      <c r="H68" s="140"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="51" t="s">
+      <c r="B69" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
+      <c r="C69" s="140"/>
+      <c r="D69" s="140"/>
+      <c r="E69" s="140"/>
+      <c r="F69" s="140"/>
+      <c r="G69" s="140"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="37"/>
@@ -3169,6 +3169,77 @@
     <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="F43:G43" name="Rango1_3"/>
   </protectedRanges>
   <mergeCells count="87">
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D37"/>
     <mergeCell ref="B9:G10"/>
@@ -3185,77 +3256,6 @@
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>

--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Documents\git\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638B3DDA-5F30-4A34-8CB4-438551E91AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696E878C-9346-486A-9E4E-36A07F673683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
@@ -839,281 +839,65 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1135,6 +919,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
@@ -1191,35 +987,239 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1964,6 +1964,56 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>839390</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>77392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>248117</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>15227</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6F95895-4891-4B8E-AE21-5D2B634DA958}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5661421" y="11090673"/>
+          <a:ext cx="516009" cy="318835"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2288,86 +2338,86 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="143" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="144" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="144"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="56" t="s">
+      <c r="D7" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
+      <c r="A8" s="146"/>
+      <c r="B8" s="146"/>
+      <c r="C8" s="146"/>
+      <c r="D8" s="146"/>
+      <c r="E8" s="146"/>
+      <c r="F8" s="146"/>
+      <c r="G8" s="146"/>
+      <c r="H8" s="146"/>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="141"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
+      <c r="B10" s="141"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="141"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="141"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
@@ -2376,22 +2426,22 @@
     </row>
     <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
+      <c r="B12" s="147"/>
+      <c r="C12" s="147"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="147"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
+      <c r="B13" s="147"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2416,10 +2466,10 @@
       <c r="A15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
+      <c r="B15" s="147"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="147"/>
       <c r="F15" s="13" t="s">
         <v>80</v>
       </c>
@@ -2428,10 +2478,10 @@
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
+      <c r="B16" s="148"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
       <c r="F16" s="13" t="s">
         <v>11</v>
       </c>
@@ -2442,14 +2492,14 @@
       <c r="A17" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="147"/>
       <c r="D17" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -2457,268 +2507,268 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
       <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="131" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="134"/>
+      <c r="F19" s="134"/>
+      <c r="G19" s="134"/>
       <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="69"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="71" t="s">
+      <c r="C20" s="136"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="71"/>
-      <c r="G20" s="72"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="129"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="59" t="s">
+      <c r="C21" s="120"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="59"/>
-      <c r="G21" s="60"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="121"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="63" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="76"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="126"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="77" t="s">
+      <c r="C23" s="120"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="71"/>
-      <c r="G23" s="72"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="129"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="59"/>
-      <c r="D24" s="60"/>
-      <c r="E24" s="58" t="s">
+      <c r="C24" s="120"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="119" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="59"/>
-      <c r="G24" s="60"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="121"/>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="78" t="s">
+      <c r="C25" s="120"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="F25" s="79"/>
-      <c r="G25" s="80"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="72"/>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24"/>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="59"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="58" t="s">
+      <c r="C26" s="120"/>
+      <c r="D26" s="121"/>
+      <c r="E26" s="119" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="59"/>
-      <c r="G26" s="60"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="121"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="81" t="s">
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="82"/>
-      <c r="G27" s="83"/>
+      <c r="F27" s="123"/>
+      <c r="G27" s="124"/>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="88"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="90" t="s">
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="91"/>
-      <c r="G28" s="92"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="104"/>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="94"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="106"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
-      <c r="B30" s="95" t="s">
+      <c r="B30" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="96"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="104" t="s">
+      <c r="C30" s="108"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="105"/>
-      <c r="G30" s="106"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="118"/>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
-      <c r="B31" s="98" t="s">
+      <c r="B31" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="99"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="46" t="s">
+      <c r="C31" s="111"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="47"/>
-      <c r="G31" s="48"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26"/>
-      <c r="B32" s="101" t="s">
+      <c r="B32" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="102"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="46" t="s">
+      <c r="C32" s="114"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="47"/>
-      <c r="G32" s="48"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="61"/>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="46" t="s">
+      <c r="B33" s="113"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="47"/>
-      <c r="G33" s="48"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="61"/>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="46" t="s">
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="47"/>
-      <c r="G34" s="48"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="61"/>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="46" t="s">
+      <c r="C35" s="60"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="47"/>
-      <c r="G35" s="48"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="61"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
-      <c r="B36" s="49" t="s">
+      <c r="B36" s="138" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="98" t="s">
+      <c r="C36" s="139"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="99"/>
-      <c r="G36" s="100"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="112"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="84" t="s">
+      <c r="B37" s="138"/>
+      <c r="C37" s="139"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="F37" s="85"/>
-      <c r="G37" s="86"/>
+      <c r="F37" s="94"/>
+      <c r="G37" s="95"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2728,9 +2778,9 @@
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="41"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="86"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="94"/>
+      <c r="G38" s="95"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2740,11 +2790,11 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44"/>
-      <c r="E39" s="107" t="s">
+      <c r="E39" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="F39" s="108"/>
-      <c r="G39" s="109"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="89"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2754,11 +2804,11 @@
       </c>
       <c r="C40" s="43"/>
       <c r="D40" s="44"/>
-      <c r="E40" s="110" t="s">
+      <c r="E40" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="111"/>
-      <c r="G40" s="112"/>
+      <c r="F40" s="91"/>
+      <c r="G40" s="92"/>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2768,11 +2818,11 @@
       </c>
       <c r="C41" s="43"/>
       <c r="D41" s="44"/>
-      <c r="E41" s="84" t="s">
+      <c r="E41" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="F41" s="85"/>
-      <c r="G41" s="86"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="95"/>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2782,9 +2832,9 @@
       </c>
       <c r="C42" s="43"/>
       <c r="D42" s="44"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="86"/>
+      <c r="E42" s="93"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="95"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2794,11 +2844,11 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44"/>
-      <c r="E43" s="46" t="s">
+      <c r="E43" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="F43" s="47"/>
-      <c r="G43" s="48"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="61"/>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2808,11 +2858,11 @@
       </c>
       <c r="C44" s="40"/>
       <c r="D44" s="41"/>
-      <c r="E44" s="113" t="s">
+      <c r="E44" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="F44" s="114"/>
-      <c r="G44" s="115"/>
+      <c r="F44" s="97"/>
+      <c r="G44" s="98"/>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2822,86 +2872,86 @@
       </c>
       <c r="C45" s="40"/>
       <c r="D45" s="41"/>
-      <c r="E45" s="116" t="s">
+      <c r="E45" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="117"/>
-      <c r="G45" s="118"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="58"/>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="73" t="s">
+      <c r="B46" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="121"/>
-      <c r="F46" s="121"/>
-      <c r="G46" s="122"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="66"/>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
-      <c r="B47" s="123" t="s">
+      <c r="B47" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="124"/>
-      <c r="D47" s="125"/>
-      <c r="E47" s="78" t="s">
+      <c r="C47" s="68"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="F47" s="79"/>
-      <c r="G47" s="80"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="72"/>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="127"/>
-      <c r="D48" s="128"/>
-      <c r="E48" s="126" t="s">
+      <c r="C48" s="74"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="127"/>
-      <c r="G48" s="128"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="75"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
-      <c r="B49" s="126" t="s">
+      <c r="B49" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="127"/>
-      <c r="D49" s="128"/>
-      <c r="E49" s="129" t="s">
+      <c r="C49" s="74"/>
+      <c r="D49" s="75"/>
+      <c r="E49" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="130"/>
-      <c r="G49" s="131"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="78"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
-      <c r="B50" s="132" t="s">
+      <c r="B50" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="C50" s="133"/>
-      <c r="D50" s="134"/>
-      <c r="E50" s="135"/>
-      <c r="F50" s="136"/>
-      <c r="G50" s="137"/>
+      <c r="C50" s="80"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="82"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="84"/>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
-      <c r="B51" s="138"/>
-      <c r="C51" s="138"/>
-      <c r="D51" s="138"/>
-      <c r="E51" s="138"/>
-      <c r="F51" s="138"/>
-      <c r="G51" s="138"/>
+      <c r="B51" s="85"/>
+      <c r="C51" s="85"/>
+      <c r="D51" s="85"/>
+      <c r="E51" s="85"/>
+      <c r="F51" s="85"/>
+      <c r="G51" s="85"/>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2909,61 +2959,61 @@
       <c r="B52" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="139"/>
-      <c r="D52" s="139"/>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
-      <c r="G52" s="139"/>
+      <c r="C52" s="86"/>
+      <c r="D52" s="86"/>
+      <c r="E52" s="86"/>
+      <c r="F52" s="86"/>
+      <c r="G52" s="86"/>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
-      <c r="B53" s="120"/>
-      <c r="C53" s="120"/>
-      <c r="D53" s="120"/>
-      <c r="E53" s="120"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="120"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
-      <c r="B54" s="120"/>
-      <c r="C54" s="120"/>
-      <c r="D54" s="120"/>
-      <c r="E54" s="120"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="120"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
-      <c r="B55" s="143"/>
-      <c r="C55" s="143"/>
-      <c r="D55" s="143"/>
-      <c r="E55" s="143"/>
-      <c r="F55" s="143"/>
-      <c r="G55" s="143"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20"/>
-      <c r="B56" s="144" t="s">
+      <c r="B56" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="144"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
       <c r="H56" s="21"/>
     </row>
     <row r="57" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
-      <c r="B57" s="145" t="s">
+      <c r="B57" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="145"/>
+      <c r="C57" s="54"/>
       <c r="D57" s="28">
         <v>7</v>
       </c>
@@ -2976,43 +3026,43 @@
     </row>
     <row r="58" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20"/>
-      <c r="B58" s="144" t="s">
+      <c r="B58" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="144"/>
-      <c r="D58" s="144"/>
-      <c r="E58" s="144"/>
-      <c r="F58" s="144"/>
-      <c r="G58" s="144"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
       <c r="H58" s="21"/>
     </row>
     <row r="59" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
-      <c r="B59" s="146" t="s">
+      <c r="B59" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="146"/>
+      <c r="C59" s="55"/>
       <c r="D59" s="30">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="148" t="s">
+      <c r="E59" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="F59" s="148"/>
+      <c r="F59" s="47"/>
       <c r="G59" s="19"/>
       <c r="H59" s="21"/>
     </row>
     <row r="60" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20"/>
-      <c r="B60" s="144" t="s">
+      <c r="B60" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="144"/>
-      <c r="D60" s="144"/>
-      <c r="E60" s="144"/>
-      <c r="F60" s="144"/>
-      <c r="G60" s="144"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
       <c r="H60" s="21"/>
     </row>
     <row r="61" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -3021,14 +3071,14 @@
         <v>63</v>
       </c>
       <c r="C61" s="31"/>
-      <c r="D61" s="147" t="s">
+      <c r="D61" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="147"/>
-      <c r="F61" s="147"/>
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
       <c r="G61" s="32">
         <f ca="1">E$17</f>
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="H61" s="21"/>
     </row>
@@ -3038,14 +3088,14 @@
         <v>64</v>
       </c>
       <c r="C62" s="33"/>
-      <c r="D62" s="147" t="s">
+      <c r="D62" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="E62" s="147"/>
-      <c r="F62" s="147"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
       <c r="G62" s="32">
         <f ca="1">E$17+8</f>
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="H62" s="21"/>
     </row>
@@ -3055,14 +3105,14 @@
         <v>65</v>
       </c>
       <c r="C63" s="33"/>
-      <c r="D63" s="147" t="s">
+      <c r="D63" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="E63" s="147"/>
-      <c r="F63" s="147"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
       <c r="G63" s="32">
         <f ca="1">E$17+35</f>
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="H63" s="34" t="s">
         <v>53</v>
@@ -3070,77 +3120,77 @@
     </row>
     <row r="64" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
-      <c r="B64" s="119" t="s">
+      <c r="B64" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="C64" s="119"/>
-      <c r="D64" s="119"/>
-      <c r="E64" s="119"/>
-      <c r="F64" s="119"/>
-      <c r="G64" s="119"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="62"/>
+      <c r="E64" s="62"/>
+      <c r="F64" s="62"/>
+      <c r="G64" s="62"/>
       <c r="H64" s="35"/>
     </row>
     <row r="65" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="142" t="s">
+      <c r="B65" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="C65" s="142"/>
-      <c r="D65" s="142"/>
-      <c r="E65" s="142"/>
-      <c r="F65" s="142"/>
-      <c r="G65" s="142"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="140" t="s">
+      <c r="B66" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="140"/>
-      <c r="D66" s="140"/>
-      <c r="E66" s="140"/>
-      <c r="F66" s="140" t="s">
+      <c r="C66" s="50"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="G66" s="140"/>
-      <c r="H66" s="140"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="50"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="141" t="s">
+      <c r="B67" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="C67" s="141"/>
-      <c r="D67" s="141"/>
-      <c r="E67" s="141"/>
-      <c r="F67" s="140" t="s">
+      <c r="C67" s="51"/>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="G67" s="140"/>
-      <c r="H67" s="140"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="141" t="s">
+      <c r="B68" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="C68" s="141"/>
-      <c r="D68" s="141"/>
-      <c r="E68" s="141"/>
-      <c r="F68" s="140" t="s">
+      <c r="C68" s="51"/>
+      <c r="D68" s="51"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="G68" s="140"/>
-      <c r="H68" s="140"/>
+      <c r="G68" s="50"/>
+      <c r="H68" s="50"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="140" t="s">
+      <c r="B69" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="140"/>
-      <c r="D69" s="140"/>
-      <c r="E69" s="140"/>
-      <c r="F69" s="140"/>
-      <c r="G69" s="140"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="37"/>
@@ -3169,26 +3219,57 @@
     <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="F43:G43" name="Rango1_3"/>
   </protectedRanges>
   <mergeCells count="87">
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D37"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="E31:G31"/>
     <mergeCell ref="E32:G32"/>
@@ -3205,57 +3286,26 @@
     <mergeCell ref="E50:G50"/>
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="C52:G52"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D37"/>
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B53:G53"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>

--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Documents\git\planos-react-app\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ProDesk\Documents\git\app-desktop-pp\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696E878C-9346-486A-9E4E-36A07F673683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F017A2-AE2D-4F44-88A4-937D80FC5C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -44,18 +44,9 @@
     <t xml:space="preserve">                                                                                                                  </t>
   </si>
   <si>
-    <t>Oficina Princ.</t>
-  </si>
-  <si>
-    <t>Oficina 2</t>
-  </si>
-  <si>
     <t>Correo:</t>
   </si>
   <si>
-    <t>PaginaWeb:</t>
-  </si>
-  <si>
     <t>COTIZACION / CONTRATO DE ELABORACIÓN EXPEDIENTE INDEPENDIZACIÓN</t>
   </si>
   <si>
@@ -245,15 +236,9 @@
     <t>www.planosperu.com.pe</t>
   </si>
   <si>
-    <t>gesstion@hotmail.com                 Whatsapp: 962303092</t>
-  </si>
-  <si>
     <t>Calle Juan José Muñoz 354 - Comas</t>
   </si>
   <si>
-    <t>Av. Guillermo Billinghurst 1081, Oficina 202 - SJM</t>
-  </si>
-  <si>
     <t>Niveles:</t>
   </si>
   <si>
@@ -345,6 +330,23 @@
   </si>
   <si>
     <t>B.26 Sucesión Intestada</t>
+  </si>
+  <si>
+    <t>Ofic.  Princ. Lima Norte</t>
+  </si>
+  <si>
+    <t>Oficina Lima Centro
+Oficina Lima Sur</t>
+  </si>
+  <si>
+    <t>José del Carmen Verástegui 273, San Juan de Miraflores
+Av. Alameda Central, Pista Este Manzana 2d Lotes 3 - 4, Cañete</t>
+  </si>
+  <si>
+    <t>gesstion@hotmail.com       Whatsapp: 962 303 092 / 906 025 864 / 906 030 445</t>
+  </si>
+  <si>
+    <t>Página Web:</t>
   </si>
 </sst>
 </file>
@@ -689,15 +691,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -839,31 +835,367 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -873,354 +1205,27 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1554,51 +1559,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>738187</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>185150</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="538162" cy="361336"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Imagen 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B596BE8B-4125-4881-AF75-18049F8A0EF6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5557837" y="747125"/>
-          <a:ext cx="538162" cy="361336"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1898,7 +1858,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1942,7 +1902,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1991,7 +1951,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2014,6 +1974,51 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>738187</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>106322</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="538162" cy="361336"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49D7B56A-C1EA-4322-A716-EA33E807650C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6015037" y="668297"/>
+          <a:ext cx="538162" cy="361336"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2322,6 +2327,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
@@ -2336,870 +2342,871 @@
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="44"/>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="C5" s="147" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="148" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+    </row>
+    <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="142" t="s">
+      <c r="D6" s="149" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="149"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="149"/>
+      <c r="H6" s="149"/>
+    </row>
+    <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+    </row>
+    <row r="9" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="43"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="43"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="16">
+        <f ca="1">TODAY()</f>
+        <v>46135</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+    </row>
+    <row r="18" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18"/>
+      <c r="B19" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="57"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="19"/>
+    </row>
+    <row r="20" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="61"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="63"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+      <c r="B21" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="47"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="143" t="s">
+      <c r="F23" s="63"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="144" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="145" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="146"/>
-      <c r="B8" s="146"/>
-      <c r="C8" s="146"/>
-      <c r="D8" s="146"/>
-      <c r="E8" s="146"/>
-      <c r="F8" s="146"/>
-      <c r="G8" s="146"/>
-      <c r="H8" s="146"/>
-    </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="141" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="141"/>
-      <c r="D9" s="141"/>
-      <c r="E9" s="141"/>
-      <c r="F9" s="141"/>
-      <c r="G9" s="141"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="141"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="141"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="147" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="147"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="10"/>
-    </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="148"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="147"/>
-      <c r="D17" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="18">
-        <f ca="1">TODAY()</f>
-        <v>46084</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="131" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="132"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="134"/>
-      <c r="F19" s="134"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="21"/>
-    </row>
-    <row r="20" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="135" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="136"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="128"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="120"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="120" t="s">
+      <c r="F24" s="47"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
+      <c r="B25" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="120"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="63" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="119" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="120"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="127" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="128"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="119" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="120"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="119" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="120"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="119" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="120"/>
-      <c r="D25" s="121"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="70" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F25" s="71"/>
       <c r="G25" s="72"/>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="26" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="119" t="s">
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="74"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="77"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="83"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="86"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22"/>
+      <c r="B29" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="23"/>
+      <c r="B30" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="120"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="119" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="120"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="59" t="s">
+      <c r="C30" s="91"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="99" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="100"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="23"/>
+      <c r="B31" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="60"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="122" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="123"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="99" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="100"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="102" t="s">
+      <c r="C31" s="94"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="97"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="97"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8"/>
+      <c r="B34" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="74"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8"/>
+      <c r="B35" s="73" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="74"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="74"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8"/>
+      <c r="B36" s="102" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="103"/>
+      <c r="D36" s="104"/>
+      <c r="E36" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="94"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8"/>
+      <c r="B37" s="102"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="103"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="107" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="108"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="116" t="s">
+      <c r="F37" s="80"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="B38" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="38"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8"/>
+      <c r="B39" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="117"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="110" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="111"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="F31" s="60"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="10"/>
-    </row>
-    <row r="32" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26"/>
-      <c r="B32" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="114"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="F32" s="60"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="10"/>
-    </row>
-    <row r="33" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="113"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="60"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="10"/>
-    </row>
-    <row r="34" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="59" t="s">
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="106"/>
+      <c r="G39" s="107"/>
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8"/>
+      <c r="B40" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="60"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="10"/>
-    </row>
-    <row r="35" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="59" t="s">
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="108" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="109"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" s="60"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="10"/>
-    </row>
-    <row r="36" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="138" t="s">
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="79" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="80"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="139"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="110" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="111"/>
-      <c r="G36" s="112"/>
-      <c r="H36" s="10"/>
-    </row>
-    <row r="37" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="138"/>
-      <c r="C37" s="139"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="93" t="s">
-        <v>84</v>
-      </c>
-      <c r="F37" s="94"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="10"/>
-    </row>
-    <row r="38" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="39" t="s">
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="8"/>
+      <c r="B43" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="93"/>
-      <c r="F38" s="94"/>
-      <c r="G38" s="95"/>
-      <c r="H38" s="10"/>
-    </row>
-    <row r="39" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="42" t="s">
+      <c r="C43" s="41"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="F43" s="74"/>
+      <c r="G43" s="75"/>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="43"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="87" t="s">
+      <c r="C44" s="38"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="111" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" s="112"/>
+      <c r="G44" s="113"/>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="8"/>
+      <c r="B45" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="38"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="114" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="115"/>
+      <c r="G45" s="116"/>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="F39" s="88"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="10"/>
-    </row>
-    <row r="40" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="43"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="90" t="s">
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="119"/>
+      <c r="G46" s="120"/>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="8"/>
+      <c r="B47" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="91"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="10"/>
-    </row>
-    <row r="41" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="93" t="s">
+      <c r="C47" s="122"/>
+      <c r="D47" s="123"/>
+      <c r="E47" s="70" t="s">
         <v>34</v>
-      </c>
-      <c r="F41" s="94"/>
-      <c r="G41" s="95"/>
-      <c r="H41" s="10"/>
-    </row>
-    <row r="42" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="C42" s="43"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="93"/>
-      <c r="F42" s="94"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="10"/>
-    </row>
-    <row r="43" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="43"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="F43" s="60"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="10"/>
-    </row>
-    <row r="44" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="96" t="s">
-        <v>85</v>
-      </c>
-      <c r="F44" s="97"/>
-      <c r="G44" s="98"/>
-      <c r="H44" s="10"/>
-    </row>
-    <row r="45" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
-      <c r="B45" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="40"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" s="57"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="10"/>
-    </row>
-    <row r="46" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="66"/>
-      <c r="H46" s="10"/>
-    </row>
-    <row r="47" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
-      <c r="B47" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="70" t="s">
-        <v>37</v>
       </c>
       <c r="F47" s="71"/>
       <c r="G47" s="72"/>
-      <c r="H47" s="10"/>
-    </row>
-    <row r="48" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
-      <c r="B48" s="73" t="s">
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8"/>
+      <c r="B48" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="125"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="124" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="125"/>
+      <c r="G48" s="126"/>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8"/>
+      <c r="B49" s="124" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="125"/>
+      <c r="D49" s="126"/>
+      <c r="E49" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="74"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="73" t="s">
+      <c r="F49" s="128"/>
+      <c r="G49" s="129"/>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
+      <c r="B50" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="10"/>
-    </row>
-    <row r="49" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
-      <c r="B49" s="73" t="s">
+      <c r="C50" s="131"/>
+      <c r="D50" s="132"/>
+      <c r="E50" s="133"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="135"/>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="8"/>
+      <c r="B51" s="136"/>
+      <c r="C51" s="136"/>
+      <c r="D51" s="136"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="136"/>
+      <c r="G51" s="136"/>
+      <c r="H51" s="8"/>
+    </row>
+    <row r="52" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8"/>
+      <c r="B52" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="74"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="76" t="s">
+      <c r="C52" s="137"/>
+      <c r="D52" s="137"/>
+      <c r="E52" s="137"/>
+      <c r="F52" s="137"/>
+      <c r="G52" s="137"/>
+      <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="8"/>
+      <c r="B53" s="118"/>
+      <c r="C53" s="118"/>
+      <c r="D53" s="118"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="8"/>
+    </row>
+    <row r="54" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8"/>
+      <c r="B54" s="118"/>
+      <c r="C54" s="118"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="118"/>
+      <c r="F54" s="118"/>
+      <c r="G54" s="118"/>
+      <c r="H54" s="8"/>
+    </row>
+    <row r="55" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="8"/>
+      <c r="B55" s="139"/>
+      <c r="C55" s="139"/>
+      <c r="D55" s="139"/>
+      <c r="E55" s="139"/>
+      <c r="F55" s="139"/>
+      <c r="G55" s="139"/>
+      <c r="H55" s="8"/>
+    </row>
+    <row r="56" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="18"/>
+      <c r="B56" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="77"/>
-      <c r="G49" s="78"/>
-      <c r="H49" s="10"/>
-    </row>
-    <row r="50" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
-      <c r="B50" s="79" t="s">
+      <c r="C56" s="140"/>
+      <c r="D56" s="140"/>
+      <c r="E56" s="140"/>
+      <c r="F56" s="140"/>
+      <c r="G56" s="140"/>
+      <c r="H56" s="19"/>
+    </row>
+    <row r="57" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="19"/>
+      <c r="B57" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="C50" s="80"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="10"/>
-    </row>
-    <row r="51" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="10"/>
-      <c r="B51" s="85"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="85"/>
-      <c r="E51" s="85"/>
-      <c r="F51" s="85"/>
-      <c r="G51" s="85"/>
-      <c r="H51" s="10"/>
-    </row>
-    <row r="52" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
-      <c r="B52" s="27" t="s">
+      <c r="C57" s="141"/>
+      <c r="D57" s="26">
+        <v>7</v>
+      </c>
+      <c r="E57" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="86"/>
-      <c r="D52" s="86"/>
-      <c r="E52" s="86"/>
-      <c r="F52" s="86"/>
-      <c r="G52" s="86"/>
-      <c r="H52" s="10"/>
-    </row>
-    <row r="53" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
-      <c r="B53" s="49"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="49"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="10"/>
-    </row>
-    <row r="54" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="49"/>
-      <c r="F54" s="49"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="10"/>
-    </row>
-    <row r="55" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="10"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="10"/>
-    </row>
-    <row r="56" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="20"/>
-      <c r="B56" s="48" t="s">
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="19"/>
+    </row>
+    <row r="58" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="18"/>
+      <c r="B58" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="21"/>
-    </row>
-    <row r="57" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="21"/>
-      <c r="B57" s="54" t="s">
+      <c r="C58" s="140"/>
+      <c r="D58" s="140"/>
+      <c r="E58" s="140"/>
+      <c r="F58" s="140"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="19"/>
+    </row>
+    <row r="59" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="19"/>
+      <c r="B59" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="54"/>
-      <c r="D57" s="28">
-        <v>7</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="21"/>
-    </row>
-    <row r="58" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20"/>
-      <c r="B58" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="21"/>
-    </row>
-    <row r="59" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="21"/>
-      <c r="B59" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="C59" s="55"/>
-      <c r="D59" s="30">
+      <c r="C59" s="142"/>
+      <c r="D59" s="28">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="47" t="s">
+      <c r="E59" s="146" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="146"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="19"/>
+    </row>
+    <row r="60" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="18"/>
+      <c r="B60" s="140" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" s="140"/>
+      <c r="D60" s="140"/>
+      <c r="E60" s="140"/>
+      <c r="F60" s="140"/>
+      <c r="G60" s="140"/>
+      <c r="H60" s="19"/>
+    </row>
+    <row r="61" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="19"/>
+      <c r="B61" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" s="29"/>
+      <c r="D61" s="143" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="143"/>
+      <c r="F61" s="143"/>
+      <c r="G61" s="30">
+        <f ca="1">E$17</f>
+        <v>46135</v>
+      </c>
+      <c r="H61" s="19"/>
+    </row>
+    <row r="62" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="19"/>
+      <c r="B62" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="31"/>
+      <c r="D62" s="143" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="143"/>
+      <c r="F62" s="143"/>
+      <c r="G62" s="30">
+        <f ca="1">E$17+8</f>
+        <v>46143</v>
+      </c>
+      <c r="H62" s="19"/>
+    </row>
+    <row r="63" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="19"/>
+      <c r="B63" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="31"/>
+      <c r="D63" s="143" t="s">
         <v>49</v>
       </c>
-      <c r="F59" s="47"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="21"/>
-    </row>
-    <row r="60" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="20"/>
-      <c r="B60" s="48" t="s">
+      <c r="E63" s="143"/>
+      <c r="F63" s="143"/>
+      <c r="G63" s="30">
+        <f ca="1">E$17+35</f>
+        <v>46170</v>
+      </c>
+      <c r="H63" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="21"/>
-    </row>
-    <row r="61" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="21"/>
-      <c r="B61" s="29" t="s">
+    </row>
+    <row r="64" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="8"/>
+      <c r="B64" s="117" t="s">
+        <v>51</v>
+      </c>
+      <c r="C64" s="117"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="117"/>
+      <c r="F64" s="117"/>
+      <c r="G64" s="117"/>
+      <c r="H64" s="33"/>
+    </row>
+    <row r="65" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="138" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" s="138"/>
+      <c r="D65" s="138"/>
+      <c r="E65" s="138"/>
+      <c r="F65" s="138"/>
+      <c r="G65" s="138"/>
+    </row>
+    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="C61" s="31"/>
-      <c r="D61" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="32">
-        <f ca="1">E$17</f>
-        <v>46084</v>
-      </c>
-      <c r="H61" s="21"/>
-    </row>
-    <row r="62" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="21"/>
-      <c r="B62" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="33"/>
-      <c r="D62" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
-      <c r="G62" s="32">
-        <f ca="1">E$17+8</f>
-        <v>46092</v>
-      </c>
-      <c r="H62" s="21"/>
-    </row>
-    <row r="63" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="21"/>
-      <c r="B63" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C63" s="33"/>
-      <c r="D63" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="32">
-        <f ca="1">E$17+35</f>
-        <v>46119</v>
-      </c>
-      <c r="H63" s="34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="10"/>
-      <c r="B64" s="62" t="s">
+      <c r="C66" s="144"/>
+      <c r="D66" s="144"/>
+      <c r="E66" s="144"/>
+      <c r="F66" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="C64" s="62"/>
-      <c r="D64" s="62"/>
-      <c r="E64" s="62"/>
-      <c r="F64" s="62"/>
-      <c r="G64" s="62"/>
-      <c r="H64" s="35"/>
-    </row>
-    <row r="65" spans="1:8" s="22" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="36" t="s">
+      <c r="G66" s="144"/>
+      <c r="H66" s="144"/>
+    </row>
+    <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="52" t="s">
+      <c r="C67" s="145"/>
+      <c r="D67" s="145"/>
+      <c r="E67" s="145"/>
+      <c r="F67" s="144" t="s">
         <v>56</v>
       </c>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
-    </row>
-    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="C66" s="50"/>
-      <c r="D66" s="50"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50" t="s">
+      <c r="G67" s="144"/>
+      <c r="H67" s="144"/>
+    </row>
+    <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="G66" s="50"/>
-      <c r="H66" s="50"/>
-    </row>
-    <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="51" t="s">
+      <c r="C68" s="145"/>
+      <c r="D68" s="145"/>
+      <c r="E68" s="145"/>
+      <c r="F68" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="50" t="s">
+      <c r="G68" s="144"/>
+      <c r="H68" s="144"/>
+    </row>
+    <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="G67" s="50"/>
-      <c r="H67" s="50"/>
-    </row>
-    <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="C68" s="51"/>
-      <c r="D68" s="51"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="G68" s="50"/>
-      <c r="H68" s="50"/>
-    </row>
-    <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="C69" s="50"/>
-      <c r="D69" s="50"/>
-      <c r="E69" s="50"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
+      <c r="C69" s="144"/>
+      <c r="D69" s="144"/>
+      <c r="E69" s="144"/>
+      <c r="F69" s="144"/>
+      <c r="G69" s="144"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
+      <c r="B70" s="35"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
     </row>
     <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3219,57 +3226,28 @@
     <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="F43:G43" name="Rango1_3"/>
   </protectedRanges>
   <mergeCells count="87">
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D37"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:H66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="E31:G31"/>
     <mergeCell ref="E32:G32"/>
@@ -3286,33 +3264,62 @@
     <mergeCell ref="E50:G50"/>
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="C52:G52"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="F66:H66"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D37"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{665AE004-2A94-48EE-BCB2-741172951D16}"/>
+    <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{8E23425C-88A5-43B7-B2BC-C8C7E44D98F6}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="87" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/backend/docs/IND.xlsx
+++ b/backend/docs/IND.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ProDesk\Documents\git\app-desktop-pp\backend\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\planos-react-app\backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F017A2-AE2D-4F44-88A4-937D80FC5C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84CA587-4977-49ED-8CBF-884FFE909420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{82C4A3E8-C4E9-43F6-AA7A-5D45B15E0799}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t xml:space="preserve">                                                                                                                  </t>
   </si>
@@ -216,9 +216,6 @@
   </si>
   <si>
     <t xml:space="preserve">Arq. Rodolfo Wilber Mogrovejo Huamani CAP N° 24431 </t>
-  </si>
-  <si>
-    <t>Ing. Sanitario José Francisco Javier Zela Steban CIP: 130333</t>
   </si>
   <si>
     <t xml:space="preserve">Cuota 1 S/  </t>
@@ -841,18 +838,355 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -861,14 +1195,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -897,335 +1223,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2342,89 +2339,89 @@
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="137" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="44"/>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="C5" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="44"/>
-    </row>
-    <row r="5" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="C5" s="147" t="s">
+      <c r="D5" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="148" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
     </row>
     <row r="6" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="149" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
+      <c r="D6" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
+        <v>100</v>
+      </c>
+      <c r="D7" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
+      <c r="A8" s="139"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="136"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="136"/>
+      <c r="E10" s="136"/>
+      <c r="F10" s="136"/>
+      <c r="G10" s="136"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="140" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
       <c r="F11" s="6" t="s">
         <v>5</v>
       </c>
@@ -2433,27 +2430,27 @@
     </row>
     <row r="12" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="140"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
+      <c r="B13" s="140"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="11" t="s">
@@ -2464,31 +2461,31 @@
         <v>7</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" s="43"/>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
+        <v>66</v>
+      </c>
+      <c r="B15" s="140"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
       <c r="F15" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="43"/>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
+      <c r="B16" s="141"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
       <c r="F16" s="11" t="s">
         <v>8</v>
       </c>
@@ -2497,16 +2494,16 @@
     </row>
     <row r="17" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
+        <v>82</v>
+      </c>
+      <c r="B17" s="140"/>
+      <c r="C17" s="140"/>
       <c r="D17" s="15" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="16">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46163</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
@@ -2514,451 +2511,451 @@
     </row>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
+      <c r="B18" s="142"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="142"/>
       <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18"/>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="57"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="146"/>
+      <c r="F19" s="146"/>
+      <c r="G19" s="146"/>
       <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="60" t="s">
+      <c r="B20" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="63" t="s">
+      <c r="C20" s="148"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="135"/>
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="47" t="s">
+      <c r="C21" s="126"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="47"/>
-      <c r="G21" s="48"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="127"/>
       <c r="H21" s="8"/>
     </row>
     <row r="22" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="68"/>
+      <c r="B22" s="66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="132"/>
       <c r="H22" s="8"/>
     </row>
     <row r="23" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="63"/>
-      <c r="G23" s="64"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="133" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="134"/>
+      <c r="G23" s="135"/>
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="125" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="F24" s="47"/>
-      <c r="G24" s="48"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="125" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="126"/>
+      <c r="G24" s="127"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21"/>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="71"/>
-      <c r="G25" s="72"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="74"/>
+      <c r="G25" s="75"/>
       <c r="H25" s="8"/>
     </row>
     <row r="26" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22"/>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="47"/>
-      <c r="G26" s="48"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="125" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="126"/>
+      <c r="G26" s="127"/>
       <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22"/>
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="74"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="76" t="s">
-        <v>72</v>
-      </c>
-      <c r="F27" s="77"/>
-      <c r="G27" s="78"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="128" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="129"/>
+      <c r="G27" s="130"/>
       <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22"/>
-      <c r="B28" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="85" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="86"/>
-      <c r="G28" s="87"/>
+      <c r="B28" s="102" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="103"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="105" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="106"/>
+      <c r="G28" s="107"/>
       <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22"/>
-      <c r="B29" s="65" t="s">
+      <c r="B29" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="89"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="109"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
-      <c r="B30" s="90" t="s">
+      <c r="B30" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="91"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="99" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" s="100"/>
-      <c r="G30" s="101"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="112"/>
+      <c r="E30" s="119" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="120"/>
+      <c r="G30" s="121"/>
       <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="23"/>
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="94"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="63"/>
+      <c r="G31" s="64"/>
       <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
-      <c r="B32" s="96" t="s">
+      <c r="B32" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="97"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="73" t="s">
+      <c r="C32" s="117"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="64"/>
       <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="96"/>
-      <c r="C33" s="97"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="73" t="s">
+      <c r="B33" s="116"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="64"/>
       <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
-      <c r="B34" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="73" t="s">
+      <c r="B34" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="63"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="64"/>
       <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
-      <c r="B35" s="73" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="73" t="s">
+      <c r="B35" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="63"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="F35" s="74"/>
-      <c r="G35" s="75"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="64"/>
       <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
-      <c r="B36" s="102" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="103"/>
-      <c r="D36" s="104"/>
-      <c r="E36" s="93" t="s">
+      <c r="B36" s="122" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="123"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="F36" s="94"/>
-      <c r="G36" s="95"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="115"/>
       <c r="H36" s="8"/>
     </row>
     <row r="37" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
-      <c r="B37" s="102"/>
-      <c r="C37" s="103"/>
-      <c r="D37" s="104"/>
-      <c r="E37" s="79" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" s="80"/>
-      <c r="G37" s="81"/>
+      <c r="B37" s="122"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="97"/>
+      <c r="G37" s="98"/>
       <c r="H37" s="8"/>
     </row>
     <row r="38" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8"/>
       <c r="B38" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C38" s="38"/>
       <c r="D38" s="39"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="81"/>
+      <c r="E38" s="96"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="98"/>
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
       <c r="B39" s="40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" s="41"/>
       <c r="D39" s="42"/>
-      <c r="E39" s="105" t="s">
+      <c r="E39" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="106"/>
-      <c r="G39" s="107"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="92"/>
       <c r="H39" s="8"/>
     </row>
     <row r="40" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
       <c r="B40" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40" s="41"/>
       <c r="D40" s="42"/>
-      <c r="E40" s="108" t="s">
+      <c r="E40" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="109"/>
-      <c r="G40" s="110"/>
+      <c r="F40" s="94"/>
+      <c r="G40" s="95"/>
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
       <c r="B41" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41" s="41"/>
       <c r="D41" s="42"/>
-      <c r="E41" s="79" t="s">
+      <c r="E41" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="F41" s="80"/>
-      <c r="G41" s="81"/>
+      <c r="F41" s="97"/>
+      <c r="G41" s="98"/>
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="42"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="81"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="97"/>
+      <c r="G42" s="98"/>
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C43" s="41"/>
       <c r="D43" s="42"/>
-      <c r="E43" s="73" t="s">
-        <v>96</v>
-      </c>
-      <c r="F43" s="74"/>
-      <c r="G43" s="75"/>
+      <c r="E43" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="F43" s="63"/>
+      <c r="G43" s="64"/>
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8"/>
       <c r="B44" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="39"/>
-      <c r="E44" s="111" t="s">
-        <v>80</v>
-      </c>
-      <c r="F44" s="112"/>
-      <c r="G44" s="113"/>
+      <c r="E44" s="99" t="s">
+        <v>79</v>
+      </c>
+      <c r="F44" s="100"/>
+      <c r="G44" s="101"/>
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8"/>
       <c r="B45" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" s="38"/>
       <c r="D45" s="39"/>
-      <c r="E45" s="114" t="s">
-        <v>81</v>
-      </c>
-      <c r="F45" s="115"/>
-      <c r="G45" s="116"/>
+      <c r="E45" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="F45" s="60"/>
+      <c r="G45" s="61"/>
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="65" t="s">
+      <c r="B46" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="66"/>
-      <c r="D46" s="66"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="120"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="69"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
-      <c r="B47" s="121" t="s">
+      <c r="B47" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="123"/>
-      <c r="E47" s="70" t="s">
+      <c r="C47" s="71"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="F47" s="71"/>
-      <c r="G47" s="72"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
       <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
-      <c r="B48" s="124" t="s">
+      <c r="B48" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="125"/>
-      <c r="D48" s="126"/>
-      <c r="E48" s="124" t="s">
+      <c r="C48" s="77"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="125"/>
-      <c r="G48" s="126"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="78"/>
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
-      <c r="B49" s="124" t="s">
+      <c r="B49" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="125"/>
-      <c r="D49" s="126"/>
-      <c r="E49" s="127" t="s">
+      <c r="C49" s="77"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="F49" s="128"/>
-      <c r="G49" s="129"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="81"/>
       <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
-      <c r="B50" s="130" t="s">
+      <c r="B50" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="131"/>
-      <c r="D50" s="132"/>
-      <c r="E50" s="133"/>
-      <c r="F50" s="134"/>
-      <c r="G50" s="135"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="85"/>
+      <c r="F50" s="86"/>
+      <c r="G50" s="87"/>
       <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="136"/>
-      <c r="C51" s="136"/>
-      <c r="D51" s="136"/>
-      <c r="E51" s="136"/>
-      <c r="F51" s="136"/>
-      <c r="G51" s="136"/>
+      <c r="B51" s="88"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="88"/>
       <c r="H51" s="8"/>
     </row>
     <row r="52" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -2966,61 +2963,61 @@
       <c r="B52" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="137"/>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137"/>
-      <c r="F52" s="137"/>
-      <c r="G52" s="137"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
+      <c r="F52" s="89"/>
+      <c r="G52" s="89"/>
       <c r="H52" s="8"/>
     </row>
     <row r="53" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
-      <c r="B53" s="118"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
       <c r="H53" s="8"/>
     </row>
     <row r="54" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
-      <c r="B54" s="118"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="118"/>
-      <c r="G54" s="118"/>
+      <c r="B54" s="47"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
       <c r="H54" s="8"/>
     </row>
     <row r="55" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
-      <c r="B55" s="139"/>
-      <c r="C55" s="139"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
       <c r="H55" s="8"/>
     </row>
     <row r="56" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="18"/>
-      <c r="B56" s="140" t="s">
+      <c r="B56" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="140"/>
-      <c r="D56" s="140"/>
-      <c r="E56" s="140"/>
-      <c r="F56" s="140"/>
-      <c r="G56" s="140"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
       <c r="H56" s="19"/>
     </row>
     <row r="57" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19"/>
-      <c r="B57" s="141" t="s">
+      <c r="B57" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="141"/>
+      <c r="C57" s="55"/>
       <c r="D57" s="26">
         <v>7</v>
       </c>
@@ -3033,93 +3030,93 @@
     </row>
     <row r="58" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
-      <c r="B58" s="140" t="s">
+      <c r="B58" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="C58" s="140"/>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="140"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
       <c r="H58" s="19"/>
     </row>
     <row r="59" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19"/>
-      <c r="B59" s="142" t="s">
+      <c r="B59" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="142"/>
+      <c r="C59" s="56"/>
       <c r="D59" s="28">
         <f>C61+C62+C63</f>
         <v>0</v>
       </c>
-      <c r="E59" s="146" t="s">
+      <c r="E59" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="F59" s="146"/>
+      <c r="F59" s="58"/>
       <c r="G59" s="17"/>
       <c r="H59" s="19"/>
     </row>
     <row r="60" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
-      <c r="B60" s="140" t="s">
+      <c r="B60" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="140"/>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="140"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
       <c r="H60" s="19"/>
     </row>
     <row r="61" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19"/>
       <c r="B61" s="27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C61" s="29"/>
-      <c r="D61" s="143" t="s">
-        <v>82</v>
-      </c>
-      <c r="E61" s="143"/>
-      <c r="F61" s="143"/>
+      <c r="D61" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
       <c r="G61" s="30">
         <f ca="1">E$17</f>
-        <v>46135</v>
+        <v>46163</v>
       </c>
       <c r="H61" s="19"/>
     </row>
     <row r="62" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="31"/>
-      <c r="D62" s="143" t="s">
+      <c r="D62" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="143"/>
-      <c r="F62" s="143"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
       <c r="G62" s="30">
         <f ca="1">E$17+8</f>
-        <v>46143</v>
+        <v>46171</v>
       </c>
       <c r="H62" s="19"/>
     </row>
     <row r="63" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19"/>
       <c r="B63" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C63" s="31"/>
-      <c r="D63" s="143" t="s">
+      <c r="D63" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="E63" s="143"/>
-      <c r="F63" s="143"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
       <c r="G63" s="30">
         <f ca="1">E$17+35</f>
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="H63" s="32" t="s">
         <v>50</v>
@@ -3127,77 +3124,75 @@
     </row>
     <row r="64" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8"/>
-      <c r="B64" s="117" t="s">
+      <c r="B64" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="C64" s="117"/>
-      <c r="D64" s="117"/>
-      <c r="E64" s="117"/>
-      <c r="F64" s="117"/>
-      <c r="G64" s="117"/>
+      <c r="C64" s="65"/>
+      <c r="D64" s="65"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="65"/>
       <c r="H64" s="33"/>
     </row>
     <row r="65" spans="1:8" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B65" s="138" t="s">
+      <c r="B65" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="C65" s="138"/>
-      <c r="D65" s="138"/>
-      <c r="E65" s="138"/>
-      <c r="F65" s="138"/>
-      <c r="G65" s="138"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="C66" s="144"/>
-      <c r="D66" s="144"/>
-      <c r="E66" s="144"/>
-      <c r="F66" s="144" t="s">
+      <c r="B66" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="50"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="G66" s="144"/>
-      <c r="H66" s="144"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="50"/>
     </row>
     <row r="67" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="145" t="s">
+      <c r="B67" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C67" s="145"/>
-      <c r="D67" s="145"/>
-      <c r="E67" s="145"/>
-      <c r="F67" s="144" t="s">
+      <c r="C67" s="51"/>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="G67" s="144"/>
-      <c r="H67" s="144"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
     </row>
     <row r="68" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="145" t="s">
+      <c r="B68" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="145"/>
-      <c r="D68" s="145"/>
-      <c r="E68" s="145"/>
-      <c r="F68" s="144" t="s">
+      <c r="C68" s="51"/>
+      <c r="D68" s="51"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="G68" s="144"/>
-      <c r="H68" s="144"/>
+      <c r="G68" s="50"/>
+      <c r="H68" s="50"/>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="144" t="s">
-        <v>59</v>
-      </c>
-      <c r="C69" s="144"/>
-      <c r="D69" s="144"/>
-      <c r="E69" s="144"/>
-      <c r="F69" s="144"/>
-      <c r="G69" s="144"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="35"/>
@@ -3226,6 +3221,77 @@
     <protectedRange algorithmName="SHA-512" hashValue="jRsd99E24Wg0cREusBHWfr8AogbmoKcBAiIEI/AkVrYZ6d3Zv1r365CvDnomnIuIagvCXHSwta3CL7/ZYpI/1A==" saltValue="4GoUJy3q9tod8g93O8nnng==" spinCount="100000" sqref="F43:G43" name="Rango1_3"/>
   </protectedRanges>
   <mergeCells count="87">
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B9:G10"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D37"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B60:G60"/>
     <mergeCell ref="B53:G53"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="D6:H6"/>
@@ -3242,84 +3308,13 @@
     <mergeCell ref="B56:G56"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D37"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B9:G10"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" display="https://www.planosperu.com.pe" xr:uid="{8E23425C-88A5-43B7-B2BC-C8C7E44D98F6}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="87" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>